--- a/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,175 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E8" s="3">
         <v>67000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>71500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>48300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>61900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>99100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>27000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7700</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -840,8 +843,8 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -879,44 +882,47 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E9" s="3">
         <v>9100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2500</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,44 +977,47 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E10" s="3">
         <v>57900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>63800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>41300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>55200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>92200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5200</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1063,8 +1072,11 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1097,100 +1109,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E12" s="3">
         <v>17100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>16500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>20800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>27400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>19200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>28700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>37400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>31400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>22300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>22900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>22000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>30800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>59300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>36100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>20600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>17200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>12600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>56400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>14000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>9300</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,8 +1297,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1334,8 +1353,8 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
@@ -1346,8 +1365,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1373,8 +1392,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1465,8 +1487,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,136 +1521,140 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>83300</v>
+      </c>
+      <c r="E17" s="3">
         <v>78000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>74600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>59500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>55800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>52700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>46300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>55500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>48300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>49300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>52900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>43200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>31900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>29400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>32600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>30400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>39300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>67600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>44100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>26200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>16300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>65400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>16200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>11400</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>46400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-23300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-36200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-30700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-40600</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1641,47 +1670,50 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>-30400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-39300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-67600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-44100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-26200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-16300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-65400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-16200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,43 +1746,44 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E20" s="3">
         <v>2500</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1900</v>
       </c>
       <c r="F20" s="3">
         <v>1900</v>
       </c>
       <c r="G20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1767,38 +1800,38 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>500</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>200</v>
       </c>
       <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
+      <c r="AD20" s="3">
+        <v>200</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
@@ -1806,44 +1839,47 @@
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>47200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-18600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-22600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-35400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-30000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-39800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1859,47 +1895,50 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-28500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-37100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-65400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-42200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-24500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-20400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-64800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1990,171 +2029,177 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>46700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-19300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-36100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-30700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-40500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-49300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-52900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-43200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-31600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-28600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-31500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-29100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-37600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-65800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-42400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-24500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-20500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-64900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E24" s="3">
         <v>5400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-16200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-177400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>-100</v>
       </c>
       <c r="AA24" s="3">
         <v>-100</v>
@@ -2163,10 +2208,10 @@
         <v>-100</v>
       </c>
       <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
       </c>
       <c r="AE24" s="3" t="s">
         <v>3</v>
@@ -2174,8 +2219,11 @@
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,192 +2314,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>224100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-36300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-41600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-49500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-53700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-43800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-37500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-26400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-31800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-27100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-37200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-65800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-42600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-64800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>224100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-36300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-41600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-49500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-53700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-43800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-37500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-26400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-31800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-27100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-37200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-65800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-42600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-64800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2599,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2598,8 +2658,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
@@ -2616,12 +2676,12 @@
       <c r="Z29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-100</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2634,8 +2694,11 @@
       <c r="AF29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2789,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,43 +2884,46 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2500</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-1900</v>
       </c>
       <c r="F32" s="3">
         <v>-1900</v>
       </c>
       <c r="G32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -2871,38 +2940,38 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-500</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-200</v>
       </c>
       <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
+      <c r="AD32" s="3">
+        <v>-200</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
@@ -2910,100 +2979,106 @@
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>224100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-36300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-41600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-49500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-53700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-43800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-37500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-26400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-31800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-27100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-37200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-65800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-42600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-64900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,197 +3169,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>224100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-36300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-41600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-49500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-53700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-43800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-37500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-26400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-31800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-27100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-37200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-65800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-42600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-64900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3401,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,83 +3436,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E41" s="3">
         <v>117800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>112600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>80600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>122700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>175800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>94300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>63300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>122500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>190200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>168000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>119900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>114000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>85900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>123500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>106300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>46900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>68800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>82800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>82600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>72000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>69700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>285500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>221100</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3443,80 +3529,83 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>98400</v>
+      </c>
+      <c r="E42" s="3">
         <v>83300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>72400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>106900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>67900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>25000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>43900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>82300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>59700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>57900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>144200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>209400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>278500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>128900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>97900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>186500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>189900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>204600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>243900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>235300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>268200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>73700</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,44 +3624,47 @@
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E43" s="3">
         <v>3000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2600</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,8 +3680,8 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -3627,47 +3719,50 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E44" s="3">
         <v>25600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>24000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>23400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>21600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2200</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3683,8 +3778,8 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -3719,83 +3814,86 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E45" s="3">
         <v>26400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1300</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3811,83 +3909,86 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>276300</v>
+      </c>
+      <c r="E46" s="3">
         <v>256100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>246000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>231500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>243100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>241800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>179900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>198800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>196400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>217500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>244800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>275600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>333200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>378400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>264500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>213100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>241600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>268300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>296500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>335000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>313800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>341500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>363900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>222500</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3903,8 +4004,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3995,83 +4099,86 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E48" s="3">
         <v>13600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>100</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4087,47 +4194,50 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E49" s="3">
         <v>17500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4143,8 +4253,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -4179,8 +4289,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4384,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,83 +4479,86 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>220100</v>
+      </c>
+      <c r="E52" s="3">
         <v>195900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>206200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>186700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>191300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>191500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6600</v>
-      </c>
-      <c r="M52" s="3">
-        <v>5800</v>
       </c>
       <c r="N52" s="3">
         <v>5800</v>
       </c>
       <c r="O52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="P52" s="3">
         <v>5600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2200</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4455,8 +4574,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,83 +4669,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>526300</v>
+      </c>
+      <c r="E54" s="3">
         <v>483100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>484300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>442900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>459700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>460000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>210600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>231000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>232800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>252900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>279200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>311200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>349500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>384400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>271400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>226100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>254500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>281800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>308100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>346200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>322000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>347100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>365100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>224800</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4639,8 +4764,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4801,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,83 +4836,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2800</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4799,8 +4929,11 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4891,83 +5024,86 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E59" s="3">
         <v>52500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>46800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>35200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>39200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>55000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>41000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>47000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>43000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>32800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>34600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>32700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>31300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>20800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>30000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>31600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>23400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>22600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>16500</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,83 +5119,86 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E60" s="3">
         <v>53500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>47500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>36600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>56500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>43500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>50400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>44800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>34400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>38800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>24900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>20600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>27600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>30200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>36900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>42600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>28000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>23100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19300</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5075,8 +5214,11 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5167,82 +5309,85 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E62" s="3">
         <v>24500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>25200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>100</v>
-      </c>
-      <c r="X62" s="3">
-        <v>200</v>
       </c>
       <c r="Y62" s="3">
         <v>200</v>
       </c>
       <c r="Z62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>0</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
@@ -5259,8 +5404,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5499,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5594,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,83 +5689,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>87500</v>
+      </c>
+      <c r="E66" s="3">
         <v>77900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>72700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>52800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>63500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>75900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>64700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>47800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>40500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>29900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>39600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>42700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>28200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19300</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5627,8 +5784,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5821,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +5914,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6009,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5917,11 +6084,11 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>310600</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5937,8 +6104,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,83 +6199,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-478000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-503200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-489300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-504300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-492000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-496500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-720600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-700600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-675400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-639100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-608500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-567000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-517500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-463800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-420000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-382500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-356100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-324300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-297200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-260000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-194200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-151600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-127200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-107000</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6121,8 +6294,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6389,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6484,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,83 +6579,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>438800</v>
+      </c>
+      <c r="E76" s="3">
         <v>405100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>411700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>390100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>396100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>384000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>153500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>166200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>185000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>214000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>235800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>270700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>311900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>358500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>250400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>205800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>225400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>251900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>275200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>306500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>279300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>318900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>341800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-105100</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6489,8 +6674,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,197 +6769,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>224100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-36300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-41600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-49500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-53700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-43800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-37500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-26400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-31800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-27100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-37200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-65800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-42600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-64900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,13 +7001,14 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
         <v>600</v>
@@ -6822,10 +7020,10 @@
         <v>600</v>
       </c>
       <c r="H83" s="3">
+        <v>600</v>
+      </c>
+      <c r="I83" s="3">
         <v>500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>700</v>
       </c>
       <c r="J83" s="3">
         <v>700</v>
@@ -6840,10 +7038,10 @@
         <v>700</v>
       </c>
       <c r="N83" s="3">
+        <v>700</v>
+      </c>
+      <c r="O83" s="3">
         <v>300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>600</v>
       </c>
       <c r="P83" s="3">
         <v>600</v>
@@ -6858,7 +7056,7 @@
         <v>600</v>
       </c>
       <c r="T83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="U83" s="3">
         <v>500</v>
@@ -6867,11 +7065,11 @@
         <v>500</v>
       </c>
       <c r="W83" s="3">
+        <v>500</v>
+      </c>
+      <c r="X83" s="3">
         <v>300</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
@@ -6887,8 +7085,8 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
@@ -6896,8 +7094,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7189,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7284,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7379,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7474,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,100 +7569,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E89" s="3">
         <v>17000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>62100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-36800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-18900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-28500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-38800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-40100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-41200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-34300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-29200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-31800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-24200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-29300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-41700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-63300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-27600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-20500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-50200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,13 +7701,14 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7503,16 +7723,16 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -7524,49 +7744,49 @@
         <v>-100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-100</v>
       </c>
       <c r="AA91" s="3">
         <v>-100</v>
       </c>
       <c r="AB91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
+      <c r="AD91" s="3">
+        <v>0</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
@@ -7574,8 +7794,11 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +7889,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,91 +7984,94 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>35500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-37900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-42700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>19000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>38300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-50000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>47800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>86000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>44800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>68600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-149700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-31200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>88800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>15200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>41400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>29700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-194900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-73900</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-100</v>
       </c>
       <c r="AA94" s="3">
         <v>-100</v>
       </c>
       <c r="AB94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
+      <c r="AD94" s="3">
+        <v>0</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
@@ -7850,8 +8079,11 @@
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,8 +8116,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7976,8 +8209,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8304,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8399,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,91 +8494,94 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>146400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>77600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>83200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>156400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>190800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>39900</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
+      <c r="AD100" s="3">
+        <v>0</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
@@ -8344,8 +8589,11 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8436,96 +8684,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E102" s="3">
         <v>5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>31900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-42100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-53000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>81500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>31000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-59100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-67700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>22000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>48100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>28200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>59400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-21900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-14000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-216100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>64600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>175800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
@@ -656,181 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E8" s="3">
         <v>83400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>67000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>71500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>48300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>61900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>99100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>27000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>32200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7700</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -846,8 +850,8 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -885,47 +889,50 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E9" s="3">
         <v>9600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2500</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -980,47 +987,50 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E10" s="3">
         <v>73800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>57900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>63800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>41300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>55200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>92200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>28000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5200</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1075,8 +1085,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1110,103 +1123,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E12" s="3">
         <v>20100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>15200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>20800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>27400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>19200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>28700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>37400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>31400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>22300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>22900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>22000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>30800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>59300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>36100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>20600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>17200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>12600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>56400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>14000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9300</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,8 +1317,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1356,8 +1376,8 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
@@ -1368,8 +1388,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1395,8 +1415,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1490,8 +1513,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1522,142 +1548,146 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E17" s="3">
         <v>83300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>78000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>74600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>59500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>55800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>52700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>55500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>42800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>48300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>49300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>52900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>43200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>31900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>32600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>30400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>39300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>67600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>44100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>26200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>16300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>65400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>16200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>11400</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E18" s="3">
         <v>100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>46400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-36200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-30700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-40600</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1673,47 +1703,50 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>-30400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-39300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-67600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-44100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-26200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-21500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-16300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-65400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-16200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-11400</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1747,46 +1780,47 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>2400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1900</v>
       </c>
       <c r="G20" s="3">
         <v>1900</v>
       </c>
       <c r="H20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1803,38 +1837,38 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>200</v>
       </c>
       <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
+      <c r="AE20" s="3">
+        <v>200</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
@@ -1842,47 +1876,50 @@
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E21" s="3">
         <v>3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>47200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-18600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-22600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-35400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-30000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-39800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1898,47 +1935,50 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-28500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-37100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-65400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-42200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-24500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-20400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-64800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2032,177 +2072,183 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>46700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-36100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-30700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-40500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-49300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-43200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-31600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-28600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-31500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-29100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-37600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-65800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-42400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-24500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-64900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-22800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-16200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-177400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-400</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>-100</v>
       </c>
       <c r="AB24" s="3">
         <v>-100</v>
@@ -2211,10 +2257,10 @@
         <v>-100</v>
       </c>
       <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
       </c>
       <c r="AF24" s="3" t="s">
         <v>3</v>
@@ -2222,8 +2268,11 @@
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2317,198 +2366,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E26" s="3">
         <v>25200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>224100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-20000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-36300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-30500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-41600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-49500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-53700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-43800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-37500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-26400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-31800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-27100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-37200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-65800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-42600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-64800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E27" s="3">
         <v>25200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>224100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-36300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-30500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-41600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-49500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-53700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-43800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-37500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-26400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-31800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-27100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-37200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-65800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-42600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-64800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2602,8 +2660,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2661,8 +2722,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>3</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>3</v>
@@ -2679,12 +2740,12 @@
       <c r="AA29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-100</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2697,8 +2758,11 @@
       <c r="AG29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2792,8 +2856,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2887,46 +2954,49 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1900</v>
       </c>
       <c r="G32" s="3">
         <v>-1900</v>
       </c>
       <c r="H32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -2943,38 +3013,38 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-200</v>
       </c>
       <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
+      <c r="AE32" s="3">
+        <v>-200</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
@@ -2982,103 +3052,109 @@
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E33" s="3">
         <v>25200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>224100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-20000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-36300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-30500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-41600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-49500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-53700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-43800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-37500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-26400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-31800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-27100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-37200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-65800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-42600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-64900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3172,203 +3248,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E35" s="3">
         <v>25200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>224100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-20000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-36300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-30500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-41600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-49500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-53700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-43800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-37500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-26400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-31800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-27100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-37200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-65800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-42600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-64900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3402,8 +3487,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3437,86 +3523,87 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>141100</v>
+      </c>
+      <c r="E41" s="3">
         <v>108000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>117800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>112600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>80600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>122700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>175800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>94300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>63300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>122500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>190200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>168000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>119900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>114000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>85900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>123500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>106300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>46900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>68800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>82800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>82600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>72000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>69700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>285500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>221100</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,83 +3619,86 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>72500</v>
+      </c>
+      <c r="E42" s="3">
         <v>98400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>83300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>72400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>106900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>67900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>25000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>43900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>82300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>59700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>57900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>144200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>209400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>278500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>128900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>97900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>186500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>189900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>204600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>243900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>235300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>268200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>73700</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3627,47 +3717,50 @@
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E43" s="3">
         <v>21300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3683,8 +3776,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -3722,50 +3815,53 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E44" s="3">
         <v>31100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>25600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>21600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2200</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3781,8 +3877,8 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3817,86 +3913,89 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E45" s="3">
         <v>17500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1300</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3912,86 +4011,89 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>270600</v>
+      </c>
+      <c r="E46" s="3">
         <v>276300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>256100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>246000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>231500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>243100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>241800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>179900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>198800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>196400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>217500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>244800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>275600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>333200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>378400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>264500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>213100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>241600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>268300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>296500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>335000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>313800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>341500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>363900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>222500</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4007,8 +4109,11 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4102,86 +4207,89 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E48" s="3">
         <v>12700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>100</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4197,50 +4305,53 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>19800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>20000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4256,8 +4367,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -4292,8 +4403,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4387,8 +4501,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4482,86 +4599,89 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E52" s="3">
         <v>220100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>195900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>206200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>186700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>191300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>191500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6600</v>
-      </c>
-      <c r="N52" s="3">
-        <v>5800</v>
       </c>
       <c r="O52" s="3">
         <v>5800</v>
       </c>
       <c r="P52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="Q52" s="3">
         <v>5600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2200</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4577,8 +4697,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4672,86 +4795,89 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>519700</v>
+      </c>
+      <c r="E54" s="3">
         <v>526300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>483100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>484300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>442900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>459700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>460000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>210600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>231000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>232800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>252900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>279200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>311200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>349500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>384400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>271400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>226100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>254500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>281800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>308100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>346200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>322000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>347100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>365100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>224800</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4767,8 +4893,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4802,8 +4931,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4837,86 +4967,87 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E57" s="3">
         <v>8200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2800</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,8 +5063,11 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5027,86 +5161,89 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E59" s="3">
         <v>55400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>52500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>46800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>35200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>39200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>55000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>41000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>47000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>43000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>32800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>34600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>32700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>31300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>22100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>21100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>20800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>30000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>31600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>23400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>22600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>16500</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5122,86 +5259,89 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E60" s="3">
         <v>63700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>36600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>47100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>56500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>50400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>44800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>38800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>35500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>20600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>19300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>27800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>27600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>30200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>36900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>42600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>28000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>23100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>19300</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5217,8 +5357,11 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5312,85 +5455,88 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E62" s="3">
         <v>23800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>100</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>200</v>
       </c>
       <c r="Z62" s="3">
         <v>200</v>
       </c>
       <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>0</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
@@ -5407,8 +5553,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5502,8 +5651,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5597,8 +5749,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5692,86 +5847,89 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E66" s="3">
         <v>87500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>77900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>72700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>52800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>75900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>57100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>64700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>47800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>43400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>40500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>21000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>29100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>29900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>32900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>39600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>42700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>28200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19300</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5787,8 +5945,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5822,8 +5983,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5917,8 +6079,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6012,8 +6177,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6087,11 +6255,11 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>310600</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -6107,8 +6275,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6202,86 +6373,89 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-495700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-478000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-503200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-489300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-504300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-492000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-496500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-720600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-700600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-675400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-639100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-608500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-567000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-517500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-463800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-420000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-382500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-356100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-324300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-297200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-260000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-194200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-151600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-127200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-107000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6297,8 +6471,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6392,8 +6569,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6487,8 +6667,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6582,86 +6765,89 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>431900</v>
+      </c>
+      <c r="E76" s="3">
         <v>438800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>405100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>411700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>390100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>396100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>384000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>153500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>166200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>185000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>214000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>235800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>270700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>311900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>358500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>250400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>205800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>225400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>251900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>275200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>306500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>279300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>318900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>341800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-105100</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6677,8 +6863,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6772,203 +6961,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E81" s="3">
         <v>25200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>224100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-20000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-36300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-30500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-41600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-49500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-53700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-43800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-37500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-26400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-31800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-27100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-37200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-65800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-42600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-64900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7002,8 +7200,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7011,7 +7210,7 @@
         <v>500</v>
       </c>
       <c r="E83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F83" s="3">
         <v>600</v>
@@ -7023,10 +7222,10 @@
         <v>600</v>
       </c>
       <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
         <v>500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>700</v>
       </c>
       <c r="K83" s="3">
         <v>700</v>
@@ -7041,10 +7240,10 @@
         <v>700</v>
       </c>
       <c r="O83" s="3">
+        <v>700</v>
+      </c>
+      <c r="P83" s="3">
         <v>300</v>
-      </c>
-      <c r="P83" s="3">
-        <v>600</v>
       </c>
       <c r="Q83" s="3">
         <v>600</v>
@@ -7059,7 +7258,7 @@
         <v>600</v>
       </c>
       <c r="U83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="V83" s="3">
         <v>500</v>
@@ -7068,11 +7267,11 @@
         <v>500</v>
       </c>
       <c r="X83" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y83" s="3">
         <v>300</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
@@ -7088,8 +7287,8 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
+      <c r="AE83" s="3">
+        <v>0</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
@@ -7097,8 +7296,11 @@
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7192,8 +7394,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7287,8 +7492,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7382,8 +7590,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7477,8 +7688,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7572,103 +7786,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>62100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-36800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-18900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-28500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-38800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-40100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-41200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-34300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-29200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-31800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-24200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-29300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-41700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-63300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-27600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-20500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-50200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7702,8 +7922,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7711,7 +7932,7 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -7726,16 +7947,16 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
@@ -7747,49 +7968,49 @@
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-100</v>
       </c>
       <c r="AB91" s="3">
         <v>-100</v>
       </c>
       <c r="AC91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
+      <c r="AE91" s="3">
+        <v>0</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
@@ -7797,8 +8018,11 @@
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7892,8 +8116,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7987,94 +8214,97 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>35500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-37900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-42700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>19000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>38300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-50000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>47800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>86000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>44800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>68600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-149700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-31200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>88800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>15200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>41400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>29700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-194900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-73900</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-100</v>
       </c>
       <c r="AB94" s="3">
         <v>-100</v>
       </c>
       <c r="AC94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
+      <c r="AE94" s="3">
+        <v>0</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
@@ -8082,8 +8312,11 @@
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8117,8 +8350,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8212,8 +8446,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8307,8 +8544,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8402,8 +8642,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8497,94 +8740,97 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>146400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>77600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>83200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>156400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>190800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>39900</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
+      <c r="AE100" s="3">
+        <v>0</v>
       </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
@@ -8592,8 +8838,11 @@
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8687,99 +8936,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>31900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-42100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-53000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>81500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>31000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-59100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-67700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>22000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>48100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>28200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-37600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>59400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-21900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-14000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-216100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>64600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>175800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
@@ -656,188 +656,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>108600</v>
+      </c>
+      <c r="E8" s="3">
         <v>79900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>83400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>67000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>71500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>48300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>61900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>99100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>27000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7700</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -853,8 +857,8 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -892,50 +896,53 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E9" s="3">
         <v>10600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2500</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -990,50 +997,53 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>96300</v>
+      </c>
+      <c r="E10" s="3">
         <v>69300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>73800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>57900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>63800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>41300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>55200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>92200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>28000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5200</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1088,8 +1098,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1124,106 +1137,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E12" s="3">
         <v>26300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>15200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>23900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>37400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>31400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>22300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>22900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>22000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>30800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>59300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>36100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>20600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>17200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>12600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>56400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>14000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9300</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,8 +1337,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1379,8 +1399,8 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
@@ -1391,8 +1411,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1418,8 +1438,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1516,8 +1539,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1549,148 +1575,152 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>108700</v>
+      </c>
+      <c r="E17" s="3">
         <v>96400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>83300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>78000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>74600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>59500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>55800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>52700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>54900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>42800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>48300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>49300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>52900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>43200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>31900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>29400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>32600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>30400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>39300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>67600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>44100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>26200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>16300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>65400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>16200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>11400</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-16500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>46400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-36200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-30700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-40600</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1706,47 +1736,50 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>-30400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-39300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-67600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-44100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-26200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-65400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-16200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-11400</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1781,49 +1814,50 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E20" s="3">
         <v>2200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1900</v>
       </c>
       <c r="H20" s="3">
         <v>1900</v>
       </c>
       <c r="I20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1840,38 +1874,38 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>500</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>200</v>
       </c>
       <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
+      <c r="AF20" s="3">
+        <v>200</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
@@ -1879,50 +1913,53 @@
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-13800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>47200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-18600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-22600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-35400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-30000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-39800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1938,47 +1975,50 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>-28500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-37100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-65400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-42200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-24500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-64800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-11200</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2075,183 +2115,189 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>46700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-23300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-36100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-30700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-40500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-49300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-52900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-43200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-31600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-28600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-31500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-29100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-37600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-65800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-42400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-24500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-64900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E24" s="3">
         <v>3400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-22800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-16200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-177400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-400</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>-100</v>
       </c>
       <c r="AC24" s="3">
         <v>-100</v>
@@ -2260,10 +2306,10 @@
         <v>-100</v>
       </c>
       <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
       </c>
       <c r="AG24" s="3" t="s">
         <v>3</v>
@@ -2271,8 +2317,11 @@
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2369,204 +2418,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>25200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>224100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-36300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-30500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-41600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-53700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-43800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-37500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-26400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-31800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-27100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-37200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-65800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-42600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-64800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>25200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>224100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-36300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-30500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-41600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-53700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-43800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-37500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-26400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-31800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-27100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-37200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-65800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-42600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-64800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2663,8 +2721,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2725,8 +2786,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>3</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>3</v>
@@ -2743,12 +2804,12 @@
       <c r="AB29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-100</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2761,8 +2822,11 @@
       <c r="AH29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2859,8 +2923,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2957,49 +3024,52 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1900</v>
       </c>
       <c r="H32" s="3">
         <v>-1900</v>
       </c>
       <c r="I32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -3016,38 +3086,38 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-500</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-200</v>
       </c>
       <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
+      <c r="AF32" s="3">
+        <v>-200</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
@@ -3055,106 +3125,112 @@
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>25200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>224100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-36300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-30500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-41600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-53700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-43800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-37500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-26400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-31800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-27100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-37200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-65800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-42600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-64900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3251,209 +3327,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>25200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>224100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-36300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-30500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-41600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-53700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-43800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-37500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-26400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-31800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-27100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-37200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-65800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-42600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-64900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3488,8 +3573,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3524,89 +3610,90 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>99300</v>
+      </c>
+      <c r="E41" s="3">
         <v>141100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>108000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>117800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>112600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>80600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>122700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>175800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>94300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>63300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>122500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>190200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>168000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>119900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>114000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>85900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>123500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>106300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>46900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>68800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>82800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>82600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>72000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>69700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>285500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>221100</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,86 +3709,89 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E42" s="3">
         <v>72500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>98400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>83300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>72400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>106900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>67900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>25000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>43900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>82300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>59700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>10000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>57900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>144200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>209400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>278500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>128900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>97900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>186500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>189900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>204600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>243900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>235300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>268200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>73700</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3720,50 +3810,53 @@
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E43" s="3">
         <v>16000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>21300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>20300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2600</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3779,8 +3872,8 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3818,53 +3911,56 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E44" s="3">
         <v>27300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>31100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>24000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>21600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>19900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2200</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3880,8 +3976,8 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
@@ -3916,89 +4012,92 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E45" s="3">
         <v>13800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>17500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1300</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4014,89 +4113,92 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E46" s="3">
         <v>270600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>276300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>256100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>246000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>231500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>243100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>241800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>179900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>198800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>196400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>217500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>244800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>275600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>333200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>378400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>264500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>213100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>241600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>268300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>296500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>335000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>313800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>341500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>363900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>222500</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4112,8 +4214,11 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4210,89 +4315,92 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E48" s="3">
         <v>13000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>100</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4308,53 +4416,56 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E49" s="3">
         <v>17000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>19500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4370,8 +4481,8 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -4406,8 +4517,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4504,8 +4618,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4602,89 +4719,92 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>212300</v>
+      </c>
+      <c r="E52" s="3">
         <v>219000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>220100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>195900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>206200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>186700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>191300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>191500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6600</v>
-      </c>
-      <c r="O52" s="3">
-        <v>5800</v>
       </c>
       <c r="P52" s="3">
         <v>5800</v>
       </c>
       <c r="Q52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="R52" s="3">
         <v>5600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2200</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4700,8 +4820,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4798,89 +4921,92 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>542400</v>
+      </c>
+      <c r="E54" s="3">
         <v>519700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>526300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>483100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>484300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>442900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>459700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>460000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>210600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>231000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>232800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>252900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>279200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>311200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>349500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>384400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>271400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>226100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>254500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>281800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>308100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>346200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>322000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>347100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>365100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>224800</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4896,8 +5022,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4932,8 +5061,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4968,89 +5098,90 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E57" s="3">
         <v>5600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2800</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5066,8 +5197,11 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5164,89 +5298,92 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E59" s="3">
         <v>58600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>55400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>52500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>46800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>35200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>39200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>55000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>41000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>47000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>43000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>32800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>32700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>31300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>22100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>21100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>20800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>30000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>31600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>23400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>16500</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5262,89 +5399,92 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E60" s="3">
         <v>64200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>63700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>47100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>56500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>43500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>50400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>44800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>35500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>31800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>20600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>27800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>27600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>30200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>36900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>42600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>28000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>23100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>19300</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5360,8 +5500,11 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5458,88 +5601,91 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E62" s="3">
         <v>23600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>23800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>19500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>100</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>200</v>
       </c>
       <c r="AA62" s="3">
         <v>200</v>
       </c>
       <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
@@ -5556,8 +5702,11 @@
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5654,8 +5803,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5752,8 +5904,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5850,89 +6005,92 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>107300</v>
+      </c>
+      <c r="E66" s="3">
         <v>87800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>87500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>77900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>72700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>63500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>75900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>57100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>64700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>47800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>43400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>21000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>29100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>29900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>32900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>39600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>42700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>28200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19300</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5948,8 +6106,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5984,8 +6145,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6082,8 +6244,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6180,8 +6345,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6258,11 +6426,11 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>310600</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
@@ -6278,8 +6446,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6376,89 +6547,92 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-499600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-495700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-478000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-503200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-489300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-504300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-492000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-496500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-720600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-700600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-675400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-639100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-608500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-567000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-517500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-463800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-420000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-382500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-356100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-324300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-297200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-260000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-194200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-151600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-127200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-107000</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6474,8 +6648,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6572,8 +6749,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6670,8 +6850,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6768,89 +6951,92 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>435100</v>
+      </c>
+      <c r="E76" s="3">
         <v>431900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>438800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>405100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>411700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>390100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>396100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>384000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>153500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>166200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>185000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>214000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>235800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>270700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>311900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>358500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>250400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>205800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>225400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>251900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>275200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>306500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>279300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>318900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>341800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-105100</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6866,8 +7052,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6964,209 +7153,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>25200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>224100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-36300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-30500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-41600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-53700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-43800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-37500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-26400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-31800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-27100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-37200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-65800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-42600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-64900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7201,19 +7399,20 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>500</v>
       </c>
       <c r="F83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
@@ -7225,10 +7424,10 @@
         <v>600</v>
       </c>
       <c r="J83" s="3">
+        <v>600</v>
+      </c>
+      <c r="K83" s="3">
         <v>500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>700</v>
       </c>
       <c r="L83" s="3">
         <v>700</v>
@@ -7243,10 +7442,10 @@
         <v>700</v>
       </c>
       <c r="P83" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q83" s="3">
         <v>300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>600</v>
       </c>
       <c r="R83" s="3">
         <v>600</v>
@@ -7261,7 +7460,7 @@
         <v>600</v>
       </c>
       <c r="V83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W83" s="3">
         <v>500</v>
@@ -7270,11 +7469,11 @@
         <v>500</v>
       </c>
       <c r="Y83" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z83" s="3">
         <v>300</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
       <c r="AA83" s="3">
         <v>0</v>
       </c>
@@ -7290,8 +7489,8 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
+      <c r="AF83" s="3">
+        <v>0</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
@@ -7299,8 +7498,11 @@
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7397,8 +7599,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7495,8 +7700,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7593,8 +7801,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7691,8 +7902,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7789,106 +8003,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E89" s="3">
         <v>4000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>62100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-36800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-18900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-38800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-40100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-41200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-34300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-29200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-31800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-24200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-29300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-41700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-63300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-27600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-20500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-50200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7923,19 +8143,20 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -7950,16 +8171,16 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
@@ -7971,49 +8192,49 @@
         <v>-100</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-100</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
       </c>
       <c r="AD91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
+      <c r="AF91" s="3">
+        <v>0</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
@@ -8021,8 +8242,11 @@
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8119,8 +8343,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8217,97 +8444,100 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="E94" s="3">
         <v>25500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>35500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-37900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-42700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>19000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>38300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-50000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>47800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>86000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>44800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>68600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-149700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-31200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>88800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>15200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>41400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>29700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-194900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-73900</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-100</v>
       </c>
       <c r="AC94" s="3">
         <v>-100</v>
       </c>
       <c r="AD94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
+      <c r="AF94" s="3">
+        <v>0</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
@@ -8315,8 +8545,11 @@
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8351,8 +8584,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8449,8 +8683,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8547,8 +8784,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8645,8 +8885,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8743,97 +8986,100 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>3600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>146400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>77600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>83200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>156400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>190800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>39900</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
+      <c r="AF100" s="3">
+        <v>0</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
@@ -8841,8 +9087,11 @@
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8939,102 +9188,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E102" s="3">
         <v>33100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>31900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-42100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-53000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>81500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>31000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-59100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-67700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>22000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>48100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>28200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-37600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>17100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>59400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-21900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-14000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>10700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-216100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>64600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>175800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>KNSA</t>
   </si>
@@ -656,195 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E8" s="3">
         <v>108600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>79900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>83400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>67000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>71500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>48300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>61900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>99100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>27000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7700</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -860,8 +864,8 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
@@ -899,53 +903,56 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>12300</v>
+        <v>49400</v>
       </c>
       <c r="E9" s="3">
-        <v>10600</v>
+        <v>42300</v>
       </c>
       <c r="F9" s="3">
-        <v>9600</v>
+        <v>31400</v>
       </c>
       <c r="G9" s="3">
-        <v>9100</v>
+        <v>26500</v>
       </c>
       <c r="H9" s="3">
-        <v>7700</v>
+        <v>26400</v>
       </c>
       <c r="I9" s="3">
-        <v>7000</v>
+        <v>21700</v>
       </c>
       <c r="J9" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K9" s="3">
         <v>6700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,53 +1007,56 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>96300</v>
+        <v>62800</v>
       </c>
       <c r="E10" s="3">
-        <v>69300</v>
+        <v>66300</v>
       </c>
       <c r="F10" s="3">
-        <v>73800</v>
+        <v>48500</v>
       </c>
       <c r="G10" s="3">
-        <v>57900</v>
+        <v>56900</v>
       </c>
       <c r="H10" s="3">
-        <v>63800</v>
+        <v>40600</v>
       </c>
       <c r="I10" s="3">
-        <v>41300</v>
+        <v>49800</v>
       </c>
       <c r="J10" s="3">
+        <v>33000</v>
+      </c>
+      <c r="K10" s="3">
         <v>55200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>92200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>28000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5200</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1101,8 +1111,11 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1138,109 +1151,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E12" s="3">
         <v>24000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>17100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>16500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>19200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>23900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>28700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>37400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>31400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>22300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>20900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>22900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>22000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>30800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>59300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>36100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>20600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>17200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>12600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>56400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>14000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>9300</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1340,31 +1357,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1402,8 +1422,8 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
@@ -1414,8 +1434,8 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1441,31 +1461,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1542,8 +1565,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1576,154 +1602,158 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>121900</v>
+      </c>
+      <c r="E17" s="3">
         <v>108700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>96400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>83300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>78000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>74600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>59500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>55800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>52700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>55500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>54900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>42800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>48300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>49300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>52900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>43200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>31900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>29400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>32600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>30400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>39300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>67600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>44100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>26200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>21500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>16300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>65400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>16200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>11400</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-11000</v>
-      </c>
       <c r="H18" s="3">
-        <v>-3100</v>
+        <v>-10900</v>
       </c>
       <c r="I18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-11200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>46400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-36200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-30700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1739,47 +1769,50 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>-30400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-39300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-67600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-44100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-26200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-21500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-16300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-65400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-11400</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1815,52 +1848,53 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2500</v>
+        <v>-2500</v>
       </c>
       <c r="E20" s="3">
-        <v>2200</v>
+        <v>-2400</v>
       </c>
       <c r="F20" s="3">
-        <v>2400</v>
+        <v>-2300</v>
       </c>
       <c r="G20" s="3">
-        <v>2500</v>
+        <v>-2400</v>
       </c>
       <c r="H20" s="3">
-        <v>1900</v>
+        <v>-2400</v>
       </c>
       <c r="I20" s="3">
-        <v>1900</v>
+        <v>-1900</v>
       </c>
       <c r="J20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1877,38 +1911,38 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3">
         <v>1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>500</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>200</v>
       </c>
       <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
+      <c r="AG20" s="3">
+        <v>200</v>
       </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
@@ -1916,53 +1950,56 @@
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E21" s="3">
         <v>2700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>47200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-22600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-35400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-30000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,70 +2015,73 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>-28500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-37100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-65400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-42200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-24500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-64800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-11200</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2118,189 +2158,195 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E23" s="3">
         <v>2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>46700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-23300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-36100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-30700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-40500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-49300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-52900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-43200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-31600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-28600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-31500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-29100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-37600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-65800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-42400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-24500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-64900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E24" s="3">
         <v>6200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-22800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-16200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-177400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-400</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>-100</v>
       </c>
       <c r="AD24" s="3">
         <v>-100</v>
@@ -2309,10 +2355,10 @@
         <v>-100</v>
       </c>
       <c r="AF24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
       </c>
       <c r="AH24" s="3" t="s">
         <v>3</v>
@@ -2320,8 +2366,11 @@
       <c r="AI24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2421,210 +2470,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>25200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>224100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-36300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-30500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-41600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-49500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-53700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-43800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-37500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-26400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-31800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-27100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-65800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-24400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-64800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>25200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>224100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-36300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-30500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-41600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-49500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-53700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-43800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-37500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-26400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-31800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-27100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-65800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-24400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-64800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2724,8 +2782,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2789,8 +2850,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>3</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>3</v>
@@ -2807,12 +2868,12 @@
       <c r="AC29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-100</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2825,8 +2886,11 @@
       <c r="AI29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2926,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3027,52 +3094,55 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2500</v>
+        <v>2500</v>
       </c>
       <c r="E32" s="3">
-        <v>-2200</v>
+        <v>2400</v>
       </c>
       <c r="F32" s="3">
-        <v>-2400</v>
+        <v>2300</v>
       </c>
       <c r="G32" s="3">
-        <v>-2500</v>
+        <v>2400</v>
       </c>
       <c r="H32" s="3">
-        <v>-1900</v>
+        <v>2400</v>
       </c>
       <c r="I32" s="3">
-        <v>-1900</v>
+        <v>1900</v>
       </c>
       <c r="J32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -3089,38 +3159,38 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3">
         <v>-1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-500</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-200</v>
       </c>
       <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
+      <c r="AG32" s="3">
+        <v>-200</v>
       </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
@@ -3128,109 +3198,115 @@
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>25200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>224100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-36300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-30500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-41600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-49500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-53700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-43800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-37500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-26400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-31800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-27100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-65800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-24400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-64900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3330,215 +3406,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>25200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>224100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-36300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-30500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-41600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-49500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-53700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-43800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-37500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-26400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-31800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-27100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-65800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-24400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-64900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3574,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3611,92 +3697,93 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>97400</v>
+      </c>
+      <c r="E41" s="3">
         <v>99300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>141100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>108000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>117800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>112600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>80600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>122700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>175800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>94300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>63300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>122500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>190200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>168000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>119900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>114000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>85900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>123500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>106300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>46900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>68800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>82800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>82600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>72000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>69700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>285500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>221100</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3712,89 +3799,92 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>126400</v>
+      </c>
+      <c r="E42" s="3">
         <v>119500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>72500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>98400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>83300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>72400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>106900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>67900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>43900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>82300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>59700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>10000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>57900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>144200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>209400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>278500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>128900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>97900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>186500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>189900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>204600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>243900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>235300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>268200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>73700</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3813,53 +3903,56 @@
       <c r="AI42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E43" s="3">
         <v>20500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>21300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2600</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3875,8 +3968,8 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -3914,56 +4007,59 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E44" s="3">
         <v>34900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>27300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>31100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>25600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>24000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>21600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2200</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3979,8 +4075,8 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
@@ -4015,92 +4111,95 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>27000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>13800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>17500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>26400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>12400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>13200</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>10500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1300</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4116,92 +4215,95 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>311300</v>
+      </c>
+      <c r="E46" s="3">
         <v>301000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>270600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>276300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>256100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>246000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>231500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>243100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>241800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>179900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>198800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>196400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>217500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>244800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>275600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>333200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>378400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>264500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>213100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>241600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>268300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>296500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>335000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>313800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>341500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>363900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>222500</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,31 +4319,34 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4318,92 +4423,95 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E48" s="3">
         <v>12400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>100</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4419,56 +4527,59 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E49" s="3">
         <v>16800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>19300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>20000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4484,8 +4595,8 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -4520,8 +4631,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4621,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4722,92 +4839,95 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>212300</v>
+        <v>7900</v>
       </c>
       <c r="E52" s="3">
-        <v>219000</v>
+        <v>7900</v>
       </c>
       <c r="F52" s="3">
-        <v>220100</v>
+        <v>4100</v>
       </c>
       <c r="G52" s="3">
-        <v>195900</v>
+        <v>800</v>
       </c>
       <c r="H52" s="3">
-        <v>206200</v>
+        <v>2300</v>
       </c>
       <c r="I52" s="3">
-        <v>186700</v>
+        <v>2400</v>
       </c>
       <c r="J52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K52" s="3">
         <v>191300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>191500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6600</v>
-      </c>
-      <c r="P52" s="3">
-        <v>5800</v>
       </c>
       <c r="Q52" s="3">
         <v>5800</v>
       </c>
       <c r="R52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="S52" s="3">
         <v>5600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2200</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4943,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4924,92 +5047,95 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>555300</v>
+      </c>
+      <c r="E54" s="3">
         <v>542400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>519700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>526300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>483100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>484300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>442900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>459700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>460000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>210600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>231000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>232800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>252900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>279200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>311200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>349500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>384400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>271400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>226100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>254500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>281800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>308100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>346200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>322000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>347100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>365100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>224800</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5025,8 +5151,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5062,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5099,92 +5229,93 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E57" s="3">
         <v>7400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2800</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5200,31 +5331,34 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5301,92 +5435,95 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>76900</v>
+        <v>16100</v>
       </c>
       <c r="E59" s="3">
-        <v>58600</v>
+        <v>11500</v>
       </c>
       <c r="F59" s="3">
-        <v>55400</v>
+        <v>11600</v>
       </c>
       <c r="G59" s="3">
-        <v>52500</v>
+        <v>8500</v>
       </c>
       <c r="H59" s="3">
-        <v>46800</v>
+        <v>9000</v>
       </c>
       <c r="I59" s="3">
-        <v>35200</v>
+        <v>9300</v>
       </c>
       <c r="J59" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K59" s="3">
         <v>39200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>55000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>41000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>47000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>43000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>32800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>34600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>32700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>31300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>21100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>20800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>30000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>31600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>23400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>22600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>16500</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5402,92 +5539,95 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E60" s="3">
         <v>84300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>64200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>63700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>47500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>36600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>47100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>56500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>43500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>50400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>44800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>34400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>35500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>31800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>20600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>19300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>27800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>27600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>30200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>36900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>42600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>28000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>23100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>19300</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5503,31 +5643,34 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>9300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>11300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5604,91 +5747,94 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="E62" s="3">
-        <v>23600</v>
+        <v>1900</v>
       </c>
       <c r="F62" s="3">
-        <v>23800</v>
+        <v>1900</v>
       </c>
       <c r="G62" s="3">
-        <v>24500</v>
+        <v>1900</v>
       </c>
       <c r="H62" s="3">
-        <v>25200</v>
+        <v>1900</v>
       </c>
       <c r="I62" s="3">
-        <v>16200</v>
+        <v>1900</v>
       </c>
       <c r="J62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K62" s="3">
         <v>16500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>100</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>200</v>
       </c>
       <c r="AB62" s="3">
         <v>200</v>
       </c>
       <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>0</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>3</v>
@@ -5705,8 +5851,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5806,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5907,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6008,92 +6163,95 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>118300</v>
+      </c>
+      <c r="E66" s="3">
         <v>107300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>87800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>87500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>77900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>72700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>63500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>75900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>64700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>47800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>43400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>25900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>21000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>20300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>29100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>29900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>32900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>39600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>42700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>28200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19300</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6109,8 +6267,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6146,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6247,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6348,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6429,11 +6597,11 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
         <v>310600</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
@@ -6449,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6550,92 +6721,95 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-512300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-499600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-495700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-478000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-503200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-489300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-504300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-492000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-496500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-720600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-700600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-675400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-639100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-608500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-567000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-517500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-463800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-420000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-382500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-356100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-324300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-297200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-260000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-194200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-151600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-127200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-107000</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6651,8 +6825,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6752,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6853,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6954,92 +7137,95 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>437000</v>
+      </c>
+      <c r="E76" s="3">
         <v>435100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>431900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>438800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>405100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>411700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>390100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>396100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>384000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>153500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>166200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>185000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>214000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>235800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>270700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>311900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>358500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>250400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>205800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>225400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>251900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>275200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>306500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>279300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>318900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>341800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-105100</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7055,8 +7241,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7156,215 +7345,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>25200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>224100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-36300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-30500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-41600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-49500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-53700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-43800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-37500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-26400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-31800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-27100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-65800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-24400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-64900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7400,37 +7598,38 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
       </c>
       <c r="H83" s="3">
+        <v>500</v>
+      </c>
+      <c r="I83" s="3">
+        <v>700</v>
+      </c>
+      <c r="J83" s="3">
+        <v>700</v>
+      </c>
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="I83" s="3">
-        <v>600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>600</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>700</v>
       </c>
       <c r="M83" s="3">
         <v>700</v>
@@ -7445,10 +7644,10 @@
         <v>700</v>
       </c>
       <c r="Q83" s="3">
+        <v>700</v>
+      </c>
+      <c r="R83" s="3">
         <v>300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>600</v>
       </c>
       <c r="S83" s="3">
         <v>600</v>
@@ -7463,7 +7662,7 @@
         <v>600</v>
       </c>
       <c r="W83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="X83" s="3">
         <v>500</v>
@@ -7472,11 +7671,11 @@
         <v>500</v>
       </c>
       <c r="Z83" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA83" s="3">
         <v>300</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
       <c r="AB83" s="3">
         <v>0</v>
       </c>
@@ -7492,8 +7691,8 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
+      <c r="AG83" s="3">
+        <v>0</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
@@ -7501,8 +7700,11 @@
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7602,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7703,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7804,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7905,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8006,109 +8220,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E89" s="3">
         <v>5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>62100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-36800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-18900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-28500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-38800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-40100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-41200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-34300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-29200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-31800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-24200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-29300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-41700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-63300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-27600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-20500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-50200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8144,8 +8364,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8153,13 +8374,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -8174,16 +8395,16 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-300</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
@@ -8195,49 +8416,49 @@
         <v>-100</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-100</v>
       </c>
       <c r="AD91" s="3">
         <v>-100</v>
       </c>
       <c r="AE91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
+      <c r="AG91" s="3">
+        <v>0</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
@@ -8245,8 +8466,11 @@
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8346,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8447,100 +8674,103 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-46800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>25500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>35500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-37900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-42700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>19000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>38300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-50000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>47800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>86000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>44800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>68600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-149700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-31200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>88800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>15200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>41400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>29700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-194900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-73900</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-100</v>
       </c>
       <c r="AD94" s="3">
         <v>-100</v>
       </c>
       <c r="AE94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
+      <c r="AG94" s="3">
+        <v>0</v>
       </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
@@ -8548,8 +8778,11 @@
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8585,31 +8818,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8686,8 +8920,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8787,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8888,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8989,100 +9232,103 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>146400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>77600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>83200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>156400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>190800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>39900</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
+      <c r="AG100" s="3">
+        <v>0</v>
       </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
@@ -9090,31 +9336,34 @@
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9191,105 +9440,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-41800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>33100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>31900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-42100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-53000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>81500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>31000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-59100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-67700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>22000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>48100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>28200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-37600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>17100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>59400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-21900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-14000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>10700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-216100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>64600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>175800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>KNSA</t>
   </si>
@@ -656,202 +656,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E8" s="3">
         <v>112200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>108600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>79900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>83400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>67000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>71500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>48300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>61900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>99100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>27000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>32200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7700</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -867,8 +870,8 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -906,56 +909,59 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E9" s="3">
         <v>49400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>42300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>31400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2500</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1010,56 +1016,59 @@
       <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E10" s="3">
         <v>62800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>66300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>48500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>56900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>40600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>49800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>55200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>92200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>22000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>28000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5200</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1114,8 +1123,11 @@
       <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1152,112 +1164,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E12" s="3">
         <v>26100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>24000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>20100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>17100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>16500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>23900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>28700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>37400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>31400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>22300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>20900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>22900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>22000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>30800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>59300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>36100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>20600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>17200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>12600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>56400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>14000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>9300</v>
       </c>
-      <c r="AH12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,8 +1376,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1386,8 +1405,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1425,8 +1444,8 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
@@ -1437,8 +1456,8 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1464,8 +1483,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1476,13 +1498,13 @@
         <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
         <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
         <v>600</v>
@@ -1491,7 +1513,7 @@
         <v>600</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1568,8 +1590,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,160 +1628,164 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>141800</v>
+      </c>
+      <c r="E17" s="3">
         <v>121900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>108700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>96400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>83300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>78000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>74600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>59500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>55800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>52700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>46300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>54900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>42800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>48300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>49300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>52900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>43200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>31900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>29400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>32600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>30400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>39300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>67600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>44100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>26200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>21500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>16300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>65400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>16200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>11400</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>46400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-23300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-36200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-40600</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1772,47 +1801,50 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-30400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-39300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-67600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-44100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-26200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-21500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-16300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-65400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-16200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1849,55 +1881,56 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2400</v>
       </c>
       <c r="H20" s="3">
         <v>-2400</v>
       </c>
       <c r="I20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1914,38 +1947,38 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>500</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>200</v>
       </c>
       <c r="AG20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>3</v>
+      <c r="AH20" s="3">
+        <v>200</v>
       </c>
       <c r="AI20" s="3" t="s">
         <v>3</v>
@@ -1953,56 +1986,59 @@
       <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>47200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-22600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-35400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-39800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,47 +2054,50 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-37100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-65400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-42200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-24500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-20400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-64800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-11200</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2083,8 +2122,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2161,195 +2200,201 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>46700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-23300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-36100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-40500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-49300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-52900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-43200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-31600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-28600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-31500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-29100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-37600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-65800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-42400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-24500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-64900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E24" s="3">
         <v>5500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-22800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-16200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-177400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-400</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>-100</v>
       </c>
       <c r="AE24" s="3">
         <v>-100</v>
@@ -2358,10 +2403,10 @@
         <v>-100</v>
       </c>
       <c r="AG24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="s">
         <v>3</v>
@@ -2369,8 +2414,11 @@
       <c r="AJ24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2473,216 +2521,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>25200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>224100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-36300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-41600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-49500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-53700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-43800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-37500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-26400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-31800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-27100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-37200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-65800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-64800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>25200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>224100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-36300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-41600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-49500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-53700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-43800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-37500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-26400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-31800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-27100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-37200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-65800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-64800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,8 +2842,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2853,8 +2913,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>3</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>3</v>
@@ -2871,12 +2931,12 @@
       <c r="AD29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-100</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2889,8 +2949,11 @@
       <c r="AJ29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3056,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,55 +3163,58 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>2500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2400</v>
       </c>
       <c r="H32" s="3">
         <v>2400</v>
       </c>
       <c r="I32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J32" s="3">
         <v>1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -3162,38 +3231,38 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-500</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-200</v>
       </c>
       <c r="AG32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>3</v>
+      <c r="AH32" s="3">
+        <v>-200</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>3</v>
@@ -3201,112 +3270,118 @@
       <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>25200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>224100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-36300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-41600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-49500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-53700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-43800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-37500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-26400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-31800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-27100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-37200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-65800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-42600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-64900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3409,221 +3484,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>25200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>224100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-36300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-41600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-49500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-53700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-43800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-37500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-26400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-31800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-27100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-37200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-65800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-42600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-64900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3660,8 +3744,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3698,95 +3783,96 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>183600</v>
+      </c>
+      <c r="E41" s="3">
         <v>97400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>141100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>108000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>117800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>112600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>80600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>122700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>175800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>94300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>63300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>122500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>190200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>168000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>119900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>114000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>85900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>123500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>106300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>46900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>68800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>82800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>82600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>72000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>69700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>285500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>221100</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3802,92 +3888,95 @@
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E42" s="3">
         <v>126400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>119500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>72500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>98400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>83300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>72400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>106900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>67900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>25000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>43900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>82300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>59700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>57900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>144200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>209400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>278500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>128900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>97900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>186500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>189900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>204600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>243900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>235300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>268200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>73700</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3906,56 +3995,59 @@
       <c r="AJ42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E43" s="3">
         <v>24900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>16000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>21300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>29400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2600</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3971,8 +4063,8 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -4010,59 +4102,62 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E44" s="3">
         <v>28700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>34900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>27300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>31100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>25600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>24000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>21600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2200</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4078,8 +4173,8 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
@@ -4114,8 +4209,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4140,69 +4238,69 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>10500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>9000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1300</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,95 +4316,98 @@
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>331800</v>
+      </c>
+      <c r="E46" s="3">
         <v>311300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>301000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>270600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>276300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>256100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>246000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>231500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>243100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>241800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>179900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>198800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>196400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>217500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>244800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>275600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>333200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>378400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>264500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>213100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>241600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>268300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>296500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>335000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>313800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>341500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>363900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>222500</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4322,8 +4423,11 @@
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4348,8 +4452,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4426,95 +4530,98 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E48" s="3">
         <v>11700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>100</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,59 +4637,62 @@
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E49" s="3">
         <v>16500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>19000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>20000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4598,8 +4708,8 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -4634,8 +4744,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4738,8 +4851,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4842,95 +4958,98 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7900</v>
+        <v>10300</v>
       </c>
       <c r="E52" s="3">
         <v>7900</v>
       </c>
       <c r="F52" s="3">
+        <v>7900</v>
+      </c>
+      <c r="G52" s="3">
         <v>4100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>191300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>191500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6600</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>5800</v>
       </c>
       <c r="R52" s="3">
         <v>5800</v>
       </c>
       <c r="S52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="T52" s="3">
         <v>5600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2200</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4946,8 +5065,11 @@
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5050,95 +5172,98 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>580600</v>
+      </c>
+      <c r="E54" s="3">
         <v>555300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>542400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>519700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>526300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>483100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>484300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>442900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>459700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>460000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>210600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>231000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>232800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>252900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>279200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>311200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>349500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>384400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>271400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>226100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>254500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>281800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>308100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>346200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>322000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>347100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>365100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>224800</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5154,8 +5279,11 @@
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5192,8 +5320,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5230,95 +5359,96 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>8300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2800</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5334,8 +5464,11 @@
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5343,10 +5476,10 @@
         <v>2000</v>
       </c>
       <c r="E58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2300</v>
       </c>
       <c r="G58" s="3">
         <v>2300</v>
@@ -5355,14 +5488,14 @@
         <v>2300</v>
       </c>
       <c r="I58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J58" s="3">
         <v>2200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5438,8 +5571,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5447,86 +5583,86 @@
         <v>16100</v>
       </c>
       <c r="E59" s="3">
+        <v>16100</v>
+      </c>
+      <c r="F59" s="3">
         <v>11500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>39200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>55000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>41000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>47000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>43000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>32800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>34600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>32700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>31300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>22100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>20800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>30000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>31600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>23400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>22600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>16500</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5542,95 +5678,98 @@
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E60" s="3">
         <v>96000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>84300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>64200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>63700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>47500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>36600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>47100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>56500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>43500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>50400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>44800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>34400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>35500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>31800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>24900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>20600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>19300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>27800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>27600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>30200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>36900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>42600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>28000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>23100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>19300</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5646,35 +5785,38 @@
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E61" s="3">
         <v>8600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5750,16 +5892,19 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1900</v>
       </c>
       <c r="F62" s="3">
         <v>1900</v>
@@ -5777,67 +5922,67 @@
         <v>1900</v>
       </c>
       <c r="K62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L62" s="3">
         <v>16500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>100</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>200</v>
       </c>
       <c r="AC62" s="3">
         <v>200</v>
       </c>
       <c r="AD62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>0</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>3</v>
@@ -5854,8 +5999,11 @@
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5958,8 +6106,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6062,8 +6213,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6166,95 +6320,98 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>142100</v>
+      </c>
+      <c r="E66" s="3">
         <v>118300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>107300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>87800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>87500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>77900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>72700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>75900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>57100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>64700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>47800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>43400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>40500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>21000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>20300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>29100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>29900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>32900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>39600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>42700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>28200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>23300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19300</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6270,8 +6427,11 @@
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6308,8 +6468,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6412,8 +6573,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6516,8 +6680,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6600,11 +6767,11 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
         <v>310600</v>
       </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
       <c r="AF70" s="3">
         <v>0</v>
       </c>
@@ -6620,8 +6787,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6724,95 +6894,98 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-521100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-512300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-499600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-495700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-478000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-503200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-489300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-504300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-492000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-496500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-720600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-700600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-675400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-639100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-608500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-567000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-517500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-463800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-420000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-382500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-356100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-324300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-297200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-194200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-151600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-127200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-107000</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6828,8 +7001,11 @@
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6932,8 +7108,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7036,8 +7215,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7140,95 +7322,98 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>438400</v>
+      </c>
+      <c r="E76" s="3">
         <v>437000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>435100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>431900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>438800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>405100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>411700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>390100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>396100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>384000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>153500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>166200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>185000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>214000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>235800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>270700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>311900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>358500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>250400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>205800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>225400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>251900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>275200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>306500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>279300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>318900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>341800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-105100</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7244,8 +7429,11 @@
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7348,221 +7536,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>25200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>224100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-36300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-41600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-49500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-53700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-43800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-37500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-26400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-31800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-27100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-37200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-65800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-42600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-64900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7599,13 +7796,14 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
         <v>600</v>
@@ -7617,22 +7815,22 @@
         <v>600</v>
       </c>
       <c r="H83" s="3">
+        <v>600</v>
+      </c>
+      <c r="I83" s="3">
         <v>500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>700</v>
       </c>
       <c r="J83" s="3">
         <v>700</v>
       </c>
       <c r="K83" s="3">
+        <v>700</v>
+      </c>
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>700</v>
       </c>
       <c r="N83" s="3">
         <v>700</v>
@@ -7647,10 +7845,10 @@
         <v>700</v>
       </c>
       <c r="R83" s="3">
+        <v>700</v>
+      </c>
+      <c r="S83" s="3">
         <v>300</v>
-      </c>
-      <c r="S83" s="3">
-        <v>600</v>
       </c>
       <c r="T83" s="3">
         <v>600</v>
@@ -7665,7 +7863,7 @@
         <v>600</v>
       </c>
       <c r="X83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Y83" s="3">
         <v>500</v>
@@ -7674,11 +7872,11 @@
         <v>500</v>
       </c>
       <c r="AA83" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB83" s="3">
         <v>300</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
-      </c>
       <c r="AC83" s="3">
         <v>0</v>
       </c>
@@ -7694,8 +7892,8 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>3</v>
+      <c r="AH83" s="3">
+        <v>0</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>3</v>
@@ -7703,8 +7901,11 @@
       <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7807,8 +8008,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7911,8 +8115,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8015,8 +8222,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8119,8 +8329,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8223,112 +8436,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>62100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-36800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-18900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-38800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-40100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-41200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-34300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-29200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-31800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-24200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-29300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-41700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-63300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-27600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-20500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-50200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8365,25 +8584,26 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -8398,16 +8618,16 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-300</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
@@ -8419,49 +8639,49 @@
         <v>-100</v>
       </c>
       <c r="T91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-100</v>
       </c>
       <c r="AE91" s="3">
         <v>-100</v>
       </c>
       <c r="AF91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>3</v>
+      <c r="AH91" s="3">
+        <v>0</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>3</v>
@@ -8469,8 +8689,11 @@
       <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8573,8 +8796,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8677,103 +8903,106 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-46800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>25500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>35500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-37900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-42700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>19000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>38300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-50000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>47800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>86000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>44800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>68600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-149700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-31200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>88800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>15200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>41400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>29700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-194900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-73900</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-100</v>
       </c>
       <c r="AE94" s="3">
         <v>-100</v>
       </c>
       <c r="AF94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>3</v>
+      <c r="AH94" s="3">
+        <v>0</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>3</v>
@@ -8781,8 +9010,11 @@
       <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8819,8 +9051,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8845,8 +9078,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8923,8 +9156,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9027,8 +9263,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9131,8 +9370,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9235,103 +9477,106 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E100" s="3">
         <v>6700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>146400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>77600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>83200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>156400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>190800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>39900</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>3</v>
+      <c r="AH100" s="3">
+        <v>0</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>3</v>
@@ -9339,8 +9584,11 @@
       <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9365,8 +9613,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9443,108 +9691,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-41800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>33100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>31900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-42100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-53000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>81500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>31000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-59100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-67700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>22000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>48100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>28200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-37600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>17100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>59400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-21900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>10700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-216100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>64600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>175800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
   <si>
     <t>KNSA</t>
   </si>
@@ -656,208 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AK7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>137800</v>
+      </c>
+      <c r="E8" s="3">
         <v>122500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>112200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>108600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>79900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>83400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>67000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>71500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>48300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>61900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>99100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>27000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7700</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,8 +877,8 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
@@ -912,59 +916,62 @@
       <c r="AK8" s="3">
         <v>0</v>
       </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>61700</v>
+      </c>
+      <c r="E9" s="3">
         <v>66100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>49400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>42300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>31400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>21700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2500</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1019,59 +1026,62 @@
       <c r="AK9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E10" s="3">
         <v>56500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>62800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>66300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>48500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>56900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>40600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>49800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>33000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>55200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>92200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>28000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5200</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1126,8 +1136,11 @@
       <c r="AK10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1165,115 +1178,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E12" s="3">
         <v>35200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>20100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>17100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>14400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>16500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>20800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>23900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>28700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>37400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>31400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>22300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>20900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>22900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>22000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>30800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>59300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>36100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>20600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>17200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>12600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>56400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>14000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>9300</v>
       </c>
-      <c r="AI12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1379,8 +1396,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1408,8 +1428,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1447,8 +1467,8 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
@@ -1459,8 +1479,8 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1486,13 +1506,16 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
         <v>400</v>
@@ -1501,13 +1524,13 @@
         <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H15" s="3">
         <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J15" s="3">
         <v>600</v>
@@ -1516,7 +1539,7 @@
         <v>600</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1593,8 +1616,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1629,166 +1655,170 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>124500</v>
+      </c>
+      <c r="E17" s="3">
         <v>141800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>121900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>108700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>96400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>83300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>78000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>74600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>59500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>54900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>42800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>48300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>49300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>52900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>43200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>31900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>29400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>32600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>30400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>39300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>67600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>44100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>26200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>21500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>16300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>65400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>16200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>11400</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-19300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>46400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-19300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-23300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-30700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-40600</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1804,47 +1834,50 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-30400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-39300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-67600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-44100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-26200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-21500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-16300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-65400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-16200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-11400</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1882,8 +1915,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1891,49 +1925,49 @@
         <v>-2300</v>
       </c>
       <c r="E20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2400</v>
       </c>
       <c r="I20" s="3">
         <v>-2400</v>
       </c>
       <c r="J20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1950,38 +1984,38 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3">
         <v>1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>500</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>200</v>
       </c>
       <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>3</v>
+      <c r="AI20" s="3">
+        <v>200</v>
       </c>
       <c r="AJ20" s="3" t="s">
         <v>3</v>
@@ -1989,59 +2023,62 @@
       <c r="AK20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-16600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-13800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>47200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-18600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-22600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-30000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-39800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2057,47 +2094,50 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-37100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-65400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-42200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-24500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-20400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-64800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-11200</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2125,8 +2165,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2203,201 +2243,207 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>46700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-23300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-30700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-40500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-49300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-52900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-43200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-31600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-28600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-31500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-29100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-37600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-65800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-42400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-24500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-64900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AI23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-8100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-22800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-16200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-177400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-400</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>-100</v>
       </c>
       <c r="AF24" s="3">
         <v>-100</v>
@@ -2406,10 +2452,10 @@
         <v>-100</v>
       </c>
       <c r="AH24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
       </c>
       <c r="AJ24" s="3" t="s">
         <v>3</v>
@@ -2417,8 +2463,11 @@
       <c r="AK24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2524,222 +2573,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>25200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>224100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-36300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-41600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-49500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-53700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-43800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-37500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-26400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-31800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-27100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-37200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-65800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-64800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>25200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>224100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-36300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-41600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-49500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-53700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-43800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-37500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-26400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-31800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-27100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-37200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-65800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-64800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2845,8 +2903,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2916,8 +2977,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>3</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>3</v>
@@ -2934,12 +2995,12 @@
       <c r="AE29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-100</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2952,8 +3013,11 @@
       <c r="AK29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3059,8 +3123,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3166,8 +3233,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3175,49 +3245,49 @@
         <v>2300</v>
       </c>
       <c r="E32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F32" s="3">
         <v>2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2400</v>
       </c>
       <c r="I32" s="3">
         <v>2400</v>
       </c>
       <c r="J32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K32" s="3">
         <v>1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -3234,38 +3304,38 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-200</v>
       </c>
       <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>3</v>
+      <c r="AI32" s="3">
+        <v>-200</v>
       </c>
       <c r="AJ32" s="3" t="s">
         <v>3</v>
@@ -3273,115 +3343,121 @@
       <c r="AK32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>25200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>224100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-36300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-41600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-49500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-53700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-43800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-37500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-26400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-31800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-27100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-37200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-65800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-42600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-64900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3487,227 +3563,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>25200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>224100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-36300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-41600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-49500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-53700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-43800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-37500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-26400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-31800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-27100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-37200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-65800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-42600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-64900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AK38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3745,8 +3830,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3784,98 +3870,99 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>157100</v>
+      </c>
+      <c r="E41" s="3">
         <v>183600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>97400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>99300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>141100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>108000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>117800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>112600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>80600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>122700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>175800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>94300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>63300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>122500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>190200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>168000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>119900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>114000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>85900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>123500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>106300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>46900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>68800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>82800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>82600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>72000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>69700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>285500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>221100</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3891,95 +3978,98 @@
       <c r="AK41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>111200</v>
+      </c>
+      <c r="E42" s="3">
         <v>60000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>126400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>119500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>72500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>98400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>83300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>72400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>106900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>67900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>25000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>43900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>82300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>59700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>10000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>57900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>144200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>209400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>278500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>128900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>97900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>186500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>189900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>204600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>243900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>235300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>268200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>73700</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,59 +4088,62 @@
       <c r="AK42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E43" s="3">
         <v>41700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2600</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4066,8 +4159,8 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -4105,62 +4198,65 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E44" s="3">
         <v>26400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>28700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>34900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>27300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>31100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>25600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>24000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>21600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>14600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>19900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2200</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4176,8 +4272,8 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA44" s="3">
         <v>0</v>
@@ -4212,8 +4308,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4241,69 +4340,69 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>10500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>14000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>9600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>9000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1300</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4319,98 +4418,101 @@
       <c r="AK45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>355900</v>
+      </c>
+      <c r="E46" s="3">
         <v>331800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>311300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>301000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>270600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>276300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>256100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>246000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>231500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>243100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>241800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>179900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>198800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>196400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>217500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>244800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>275600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>333200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>378400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>264500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>213100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>241600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>268300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>296500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>335000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>313800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>341500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>363900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>222500</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4426,8 +4528,11 @@
       <c r="AK46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4455,8 +4560,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4533,98 +4638,101 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E48" s="3">
         <v>11000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>100</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4640,62 +4748,65 @@
       <c r="AK48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E49" s="3">
         <v>16300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>20000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4711,8 +4822,8 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -4747,8 +4858,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4854,8 +4968,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4961,98 +5078,101 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E52" s="3">
         <v>10300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>7900</v>
       </c>
       <c r="F52" s="3">
         <v>7900</v>
       </c>
       <c r="G52" s="3">
+        <v>7900</v>
+      </c>
+      <c r="H52" s="3">
         <v>4100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>191300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>191500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6600</v>
-      </c>
-      <c r="R52" s="3">
-        <v>5800</v>
       </c>
       <c r="S52" s="3">
         <v>5800</v>
       </c>
       <c r="T52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="U52" s="3">
         <v>5600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2200</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5068,8 +5188,11 @@
       <c r="AK52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5175,98 +5298,101 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>599300</v>
+      </c>
+      <c r="E54" s="3">
         <v>580600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>555300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>542400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>519700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>526300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>483100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>484300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>442900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>459700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>460000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>210600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>231000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>232800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>252900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>279200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>311200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>349500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>384400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>271400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>226100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>254500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>281800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>308100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>346200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>322000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>347100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>365100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>224800</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5282,8 +5408,11 @@
       <c r="AK54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5321,8 +5450,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5360,8 +5490,9 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5369,89 +5500,89 @@
         <v>2000</v>
       </c>
       <c r="E57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F57" s="3">
         <v>8300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2800</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,22 +5598,25 @@
       <c r="AK57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="E58" s="3">
         <v>2000</v>
       </c>
       <c r="F58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G58" s="3">
         <v>2100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2300</v>
       </c>
       <c r="H58" s="3">
         <v>2300</v>
@@ -5491,14 +5625,14 @@
         <v>2300</v>
       </c>
       <c r="J58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5574,98 +5708,101 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>16100</v>
+        <v>17100</v>
       </c>
       <c r="E59" s="3">
         <v>16100</v>
       </c>
       <c r="F59" s="3">
+        <v>16100</v>
+      </c>
+      <c r="G59" s="3">
         <v>11500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>39200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>55000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>41000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>47000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>43000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>32800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>34600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>32700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>31300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>21000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>22100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>20800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>30000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>31600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>23400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>22600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>16500</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5681,98 +5818,101 @@
       <c r="AK59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E60" s="3">
         <v>100600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>96000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>84300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>64200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>63700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>47500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>36600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>47100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>56500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>43500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>50400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>44800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>34400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>35500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>31800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>24900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>20600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>19300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>27800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>27600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>30200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>36900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>42600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>28000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>23100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>19300</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5788,38 +5928,41 @@
       <c r="AK60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E61" s="3">
         <v>7900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5895,19 +6038,22 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1900</v>
       </c>
       <c r="G62" s="3">
         <v>1900</v>
@@ -5925,67 +6071,67 @@
         <v>1900</v>
       </c>
       <c r="L62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M62" s="3">
         <v>16500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>19500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>100</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>200</v>
       </c>
       <c r="AD62" s="3">
         <v>200</v>
       </c>
       <c r="AE62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF62" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>3</v>
@@ -6002,8 +6148,11 @@
       <c r="AK62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6109,8 +6258,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6216,8 +6368,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6323,98 +6478,101 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>141800</v>
+      </c>
+      <c r="E66" s="3">
         <v>142100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>118300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>107300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>87800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>87500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>77900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>72700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>63500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>75900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>57100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>64700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>47800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>38800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>43400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>40500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>37500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>25900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>21000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>20300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>29100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>29900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>32900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>39600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>42700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>28200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19300</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6430,8 +6588,11 @@
       <c r="AK66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6469,8 +6630,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6576,8 +6738,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6683,8 +6848,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6770,11 +6938,11 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
         <v>310600</v>
       </c>
-      <c r="AF70" s="3">
-        <v>0</v>
-      </c>
       <c r="AG70" s="3">
         <v>0</v>
       </c>
@@ -6790,8 +6958,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6897,98 +7068,101 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-512600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-521100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-512300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-499600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-495700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-478000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-503200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-489300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-504300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-492000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-496500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-720600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-700600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-675400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-639100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-608500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-567000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-517500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-463800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-420000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-382500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-356100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-324300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-297200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-194200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-151600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-127200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-107000</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7004,8 +7178,11 @@
       <c r="AK72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7111,8 +7288,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7218,8 +7398,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7325,98 +7508,101 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>457500</v>
+      </c>
+      <c r="E76" s="3">
         <v>438400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>437000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>435100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>431900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>438800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>405100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>411700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>390100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>396100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>384000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>153500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>166200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>185000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>214000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>235800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>270700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>311900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>358500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>250400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>205800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>225400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>251900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>275200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>306500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>279300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>318900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>341800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-105100</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7432,8 +7618,11 @@
       <c r="AK76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7539,227 +7728,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AK80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>25200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>224100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-36300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-41600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-49500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-53700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-43800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-37500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-26400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-31800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-27100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-37200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-65800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-42600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-64900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7797,8 +7995,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7806,7 +8005,7 @@
         <v>500</v>
       </c>
       <c r="E83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F83" s="3">
         <v>600</v>
@@ -7818,22 +8017,22 @@
         <v>600</v>
       </c>
       <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
         <v>500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>700</v>
       </c>
       <c r="K83" s="3">
         <v>700</v>
       </c>
       <c r="L83" s="3">
+        <v>700</v>
+      </c>
+      <c r="M83" s="3">
         <v>600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>700</v>
       </c>
       <c r="O83" s="3">
         <v>700</v>
@@ -7848,10 +8047,10 @@
         <v>700</v>
       </c>
       <c r="S83" s="3">
+        <v>700</v>
+      </c>
+      <c r="T83" s="3">
         <v>300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>600</v>
       </c>
       <c r="U83" s="3">
         <v>600</v>
@@ -7866,7 +8065,7 @@
         <v>600</v>
       </c>
       <c r="Y83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Z83" s="3">
         <v>500</v>
@@ -7875,11 +8074,11 @@
         <v>500</v>
       </c>
       <c r="AB83" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC83" s="3">
         <v>300</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
       <c r="AD83" s="3">
         <v>0</v>
       </c>
@@ -7895,8 +8094,8 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>3</v>
+      <c r="AI83" s="3">
+        <v>0</v>
       </c>
       <c r="AJ83" s="3" t="s">
         <v>3</v>
@@ -7904,8 +8103,11 @@
       <c r="AK83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8011,8 +8213,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8118,8 +8323,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8225,8 +8433,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8332,8 +8543,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8439,115 +8653,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E89" s="3">
         <v>18800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>62100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-36800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-28500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-38800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-40100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-41200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-34300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-29200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-31800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-24200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-29300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-41700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-63300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-27600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-20500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-50200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8585,28 +8805,29 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -8621,16 +8842,16 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
@@ -8642,49 +8863,49 @@
         <v>-100</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-100</v>
       </c>
       <c r="AF91" s="3">
         <v>-100</v>
       </c>
       <c r="AG91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>3</v>
+      <c r="AI91" s="3">
+        <v>0</v>
       </c>
       <c r="AJ91" s="3" t="s">
         <v>3</v>
@@ -8692,8 +8913,11 @@
       <c r="AK91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8799,8 +9023,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8906,106 +9133,109 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-51500</v>
+      </c>
+      <c r="E94" s="3">
         <v>65300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-46800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>25500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>35500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-37900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-42700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>38300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-50000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>47800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>86000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>44800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>68600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-149700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-31200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>88800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>15200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>41400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>29700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-194900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-73900</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>-100</v>
       </c>
       <c r="AF94" s="3">
         <v>-100</v>
       </c>
       <c r="AG94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>3</v>
+      <c r="AI94" s="3">
+        <v>0</v>
       </c>
       <c r="AJ94" s="3" t="s">
         <v>3</v>
@@ -9013,8 +9243,11 @@
       <c r="AK94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9052,8 +9285,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9081,8 +9315,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9159,8 +9393,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9266,8 +9503,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9373,8 +9613,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9480,106 +9723,109 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E100" s="3">
         <v>2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>146400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>77600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>83200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>156400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>190800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>39900</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>3</v>
+      <c r="AI100" s="3">
+        <v>0</v>
       </c>
       <c r="AJ100" s="3" t="s">
         <v>3</v>
@@ -9587,8 +9833,11 @@
       <c r="AK100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9616,8 +9865,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9694,111 +9943,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="E102" s="3">
         <v>86200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-41800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>33100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>31900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-42100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-53000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>81500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>31000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-59100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-67700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>22000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>48100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>28200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-37600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>17100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>59400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-21900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>10700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-216100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>64600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>175800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="92">
   <si>
     <t>KNSA</t>
   </si>
@@ -656,215 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="39" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AK7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AL7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AM7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>156800</v>
+      </c>
+      <c r="E8" s="3">
         <v>137800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>122500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>112200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>108600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>79900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>83400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>67000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>71500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>48300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>61900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>99100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>27000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>32200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7700</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -880,8 +884,8 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
@@ -919,62 +923,65 @@
       <c r="AL8" s="3">
         <v>0</v>
       </c>
+      <c r="AM8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E9" s="3">
         <v>61700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>66100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>49400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>42300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>31400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2500</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,62 +1036,65 @@
       <c r="AL9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E10" s="3">
         <v>76100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>56500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>62800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>66300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>48500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>56900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>40600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>49800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>33000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>55200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>92200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>28000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5200</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1139,8 +1149,11 @@
       <c r="AL10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1179,118 +1192,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E12" s="3">
         <v>19300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>35200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>20100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>17100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>14400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>16500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>20800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>27400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>19200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>23900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>28700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>37400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>31400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>22300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>20900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>22900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>22000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>30800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>59300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>36100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>20600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>17200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>12600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>56400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>14000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1399,8 +1416,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1431,8 +1451,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1470,8 +1490,8 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
@@ -1482,8 +1502,8 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1509,16 +1529,19 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>400</v>
+      </c>
+      <c r="E15" s="3">
         <v>300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>400</v>
       </c>
       <c r="F15" s="3">
         <v>400</v>
@@ -1527,13 +1550,13 @@
         <v>400</v>
       </c>
       <c r="H15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I15" s="3">
         <v>500</v>
       </c>
       <c r="J15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
@@ -1542,7 +1565,7 @@
         <v>600</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1619,8 +1642,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1656,172 +1682,176 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E17" s="3">
         <v>124500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>141800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>121900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>108700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>96400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>83300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>78000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>74600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>59500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>55800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>52700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>54900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>42800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>48300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>49300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>52900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>43200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>31900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>29400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>32600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>30400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>39300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>67600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>44100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>26200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>16300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>65400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>16200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>11400</v>
       </c>
-      <c r="AJ17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E18" s="3">
         <v>13300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-19300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>46400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-36200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-30700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-40600</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1837,47 +1867,50 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-30400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-39300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-67600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-44100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-26200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-21500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-16300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-65400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-16200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-11400</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1916,61 +1949,62 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2300</v>
+        <v>-2700</v>
       </c>
       <c r="E20" s="3">
         <v>-2300</v>
       </c>
       <c r="F20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G20" s="3">
         <v>-2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-2400</v>
       </c>
       <c r="J20" s="3">
         <v>-2400</v>
       </c>
       <c r="K20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1987,38 +2021,38 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3">
         <v>1400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>500</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>200</v>
       </c>
       <c r="AI20" s="3">
         <v>200</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>3</v>
+      <c r="AJ20" s="3">
+        <v>200</v>
       </c>
       <c r="AK20" s="3" t="s">
         <v>3</v>
@@ -2026,62 +2060,65 @@
       <c r="AL20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E21" s="3">
         <v>15900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-16600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-13800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>47200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-18600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-35400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-30000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-39800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2097,47 +2134,50 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-28500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-37100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-65400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-42200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-24500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-20400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-64800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-11200</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2168,8 +2208,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2246,207 +2286,213 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E23" s="3">
         <v>15600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>46700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-36100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-30700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-40500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-49300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-52900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-43200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-31600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-28600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-31500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-29100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-37600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-65800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-42400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-24500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-64900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AJ23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>7000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-8100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-22800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-16200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-177400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-400</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>-100</v>
       </c>
       <c r="AG24" s="3">
         <v>-100</v>
@@ -2455,10 +2501,10 @@
         <v>-100</v>
       </c>
       <c r="AI24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="s">
         <v>3</v>
@@ -2466,8 +2512,11 @@
       <c r="AL24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2576,228 +2625,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E26" s="3">
         <v>8500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>25200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>224100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-20000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-36300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-30500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-41600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-49500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-53700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-43800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-37500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-26400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-31800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-27100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-37200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-65800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-24400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-64800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AJ26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E27" s="3">
         <v>8500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>25200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>15000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>224100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-36300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-30500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-41600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-49500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-53700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-43800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-37500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-26400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-31800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-27100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-37200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-65800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-24400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-64800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AJ27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2906,8 +2964,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2980,8 +3041,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>3</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>3</v>
@@ -2998,12 +3059,12 @@
       <c r="AF29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-100</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>3</v>
       </c>
@@ -3016,8 +3077,11 @@
       <c r="AL29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3126,8 +3190,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3236,61 +3303,64 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2300</v>
+        <v>2700</v>
       </c>
       <c r="E32" s="3">
         <v>2300</v>
       </c>
       <c r="F32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G32" s="3">
         <v>2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2400</v>
       </c>
       <c r="J32" s="3">
         <v>2400</v>
       </c>
       <c r="K32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L32" s="3">
         <v>1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -3307,38 +3377,38 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-500</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-200</v>
       </c>
       <c r="AI32" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>3</v>
+      <c r="AJ32" s="3">
+        <v>-200</v>
       </c>
       <c r="AK32" s="3" t="s">
         <v>3</v>
@@ -3346,118 +3416,124 @@
       <c r="AL32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E33" s="3">
         <v>8500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>25200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>224100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-36300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-30500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-41600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-49500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-53700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-43800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-37500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-26400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-31800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-27100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-37200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-65800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-42600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-24400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-64900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AJ33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3566,233 +3642,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E35" s="3">
         <v>8500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>25200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>224100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-36300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-30500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-41600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-49500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-53700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-43800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-37500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-26400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-31800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-27100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-37200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-65800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-42600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-24400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-64900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AJ35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AK38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AL38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AM38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3831,8 +3916,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3871,101 +3957,102 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E41" s="3">
         <v>157100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>183600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>97400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>99300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>141100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>108000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>117800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>112600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>80600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>122700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>175800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>94300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>63300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>122500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>190200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>168000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>119900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>114000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>85900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>123500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>106300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>46900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>68800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>82800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>82600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>72000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>69700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>285500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>221100</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3981,98 +4068,101 @@
       <c r="AL41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>115700</v>
+      </c>
+      <c r="E42" s="3">
         <v>111200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>60000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>126400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>119500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>72500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>98400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>83300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>72400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>106900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>67900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>25000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>43900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>82300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>59700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>10000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>57900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>144200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>209400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>278500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>128900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>97900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>186500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>189900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>204600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>243900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>235300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>268200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>73700</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4091,62 +4181,65 @@
       <c r="AL42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E43" s="3">
         <v>40100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>41700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>29400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2600</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4162,8 +4255,8 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -4201,65 +4294,68 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E44" s="3">
         <v>22100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>28700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>34900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>27300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>31100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>25600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>24000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>23400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>21600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>14600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>19900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2200</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4275,8 +4371,8 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB44" s="3">
         <v>0</v>
@@ -4311,8 +4407,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4343,69 +4442,69 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>10500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>9600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>9000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1300</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4421,101 +4520,104 @@
       <c r="AL45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>420300</v>
+      </c>
+      <c r="E46" s="3">
         <v>355900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>331800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>311300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>301000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>270600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>276300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>256100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>246000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>231500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>243100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>241800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>179900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>198800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>196400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>217500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>244800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>275600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>333200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>378400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>264500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>213100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>241600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>268300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>296500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>335000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>313800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>341500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>363900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>222500</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,8 +4633,11 @@
       <c r="AL46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4563,8 +4668,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4641,101 +4746,104 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E48" s="3">
         <v>11100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>100</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4751,65 +4859,68 @@
       <c r="AL48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E49" s="3">
         <v>16000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>20000</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +4936,8 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
@@ -4861,8 +4972,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4971,8 +5085,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5081,8 +5198,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5090,92 +5210,92 @@
         <v>8200</v>
       </c>
       <c r="E52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F52" s="3">
         <v>10300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>7900</v>
       </c>
       <c r="G52" s="3">
         <v>7900</v>
       </c>
       <c r="H52" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I52" s="3">
         <v>4100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>191300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>191500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6600</v>
-      </c>
-      <c r="S52" s="3">
-        <v>5800</v>
       </c>
       <c r="T52" s="3">
         <v>5800</v>
       </c>
       <c r="U52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="V52" s="3">
         <v>5600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2200</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5191,8 +5311,11 @@
       <c r="AL52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5301,101 +5424,104 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>661200</v>
+      </c>
+      <c r="E54" s="3">
         <v>599300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>580600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>555300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>542400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>519700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>526300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>483100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>484300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>442900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>459700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>460000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>210600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>231000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>232800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>252900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>279200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>311200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>349500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>384400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>271400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>226100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>254500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>281800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>308100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>346200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>322000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>347100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>365100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>224800</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5411,8 +5537,11 @@
       <c r="AL54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5451,8 +5580,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5491,101 +5621,102 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="E57" s="3">
         <v>2000</v>
       </c>
       <c r="F57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G57" s="3">
         <v>8300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2800</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5601,25 +5732,28 @@
       <c r="AL57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2300</v>
-      </c>
-      <c r="E58" s="3">
-        <v>2000</v>
       </c>
       <c r="F58" s="3">
         <v>2000</v>
       </c>
       <c r="G58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H58" s="3">
         <v>2100</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2300</v>
       </c>
       <c r="I58" s="3">
         <v>2300</v>
@@ -5628,14 +5762,14 @@
         <v>2300</v>
       </c>
       <c r="K58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L58" s="3">
         <v>2200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3500</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5711,101 +5845,104 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E59" s="3">
         <v>17100</v>
-      </c>
-      <c r="E59" s="3">
-        <v>16100</v>
       </c>
       <c r="F59" s="3">
         <v>16100</v>
       </c>
       <c r="G59" s="3">
+        <v>16100</v>
+      </c>
+      <c r="H59" s="3">
         <v>11500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>39200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>55000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>41000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>47000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>43000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>32800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>34600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>32700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>31300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>21000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>22100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>21100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>20800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>30000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>31600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>23400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>22600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>16500</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5821,101 +5958,104 @@
       <c r="AL59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>117800</v>
+      </c>
+      <c r="E60" s="3">
         <v>97300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>100600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>96000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>84300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>64200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>63700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>53500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>47500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>36600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>47100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>56500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>43500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>50400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>44800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>34400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>35500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>31800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>24900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>20600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>19300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>27800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>27600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>30200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>36900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>42600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>28000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>23100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>19300</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5931,41 +6071,44 @@
       <c r="AL60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E61" s="3">
         <v>7600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -6041,22 +6184,25 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E62" s="3">
         <v>5100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1900</v>
       </c>
       <c r="H62" s="3">
         <v>1900</v>
@@ -6074,67 +6220,67 @@
         <v>1900</v>
       </c>
       <c r="M62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N62" s="3">
         <v>16500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>19500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>100</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>200</v>
       </c>
       <c r="AE62" s="3">
         <v>200</v>
       </c>
       <c r="AF62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG62" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>3</v>
@@ -6151,8 +6297,11 @@
       <c r="AL62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6261,8 +6410,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6371,8 +6523,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6481,101 +6636,104 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>166100</v>
+      </c>
+      <c r="E66" s="3">
         <v>141800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>142100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>118300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>107300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>87800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>87500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>77900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>72700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>63500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>75900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>57100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>64700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>47800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>43400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>40500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>37500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>25900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>21000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>29100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>29900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>32900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>39600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>42700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>28200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>23300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19300</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6591,8 +6749,11 @@
       <c r="AL66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6631,8 +6792,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6741,8 +6903,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6851,8 +7016,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6941,11 +7109,11 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
         <v>310600</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
       <c r="AH70" s="3">
         <v>0</v>
       </c>
@@ -6961,8 +7129,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7071,101 +7242,104 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-494800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-512600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-521100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-512300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-499600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-495700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-478000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-503200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-489300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-504300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-492000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-496500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-720600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-700600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-675400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-639100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-608500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-567000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-517500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-463800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-420000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-382500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-356100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-324300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-297200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-194200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-151600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-127200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-107000</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7181,8 +7355,11 @@
       <c r="AL72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7291,8 +7468,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7401,8 +7581,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7511,101 +7694,104 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>495000</v>
+      </c>
+      <c r="E76" s="3">
         <v>457500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>438400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>437000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>435100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>431900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>438800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>405100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>411700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>390100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>396100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>384000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>153500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>166200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>185000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>214000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>235800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>270700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>311900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>358500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>250400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>205800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>225400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>251900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>275200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>306500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>279300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>318900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>341800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-105100</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7621,8 +7807,11 @@
       <c r="AL76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7731,233 +7920,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AK80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AL80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AM80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E81" s="3">
         <v>8500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>25200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>224100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-36300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-30500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-41600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-49500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-53700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-43800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-37500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-26400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-31800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-27100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-37200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-65800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-42600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-24400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-64900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AJ81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7996,19 +8194,20 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>500</v>
       </c>
       <c r="F83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
@@ -8020,22 +8219,22 @@
         <v>600</v>
       </c>
       <c r="J83" s="3">
+        <v>600</v>
+      </c>
+      <c r="K83" s="3">
         <v>500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>700</v>
       </c>
       <c r="L83" s="3">
         <v>700</v>
       </c>
       <c r="M83" s="3">
+        <v>700</v>
+      </c>
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>700</v>
@@ -8050,10 +8249,10 @@
         <v>700</v>
       </c>
       <c r="T83" s="3">
+        <v>700</v>
+      </c>
+      <c r="U83" s="3">
         <v>300</v>
-      </c>
-      <c r="U83" s="3">
-        <v>600</v>
       </c>
       <c r="V83" s="3">
         <v>600</v>
@@ -8068,7 +8267,7 @@
         <v>600</v>
       </c>
       <c r="Z83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AA83" s="3">
         <v>500</v>
@@ -8077,11 +8276,11 @@
         <v>500</v>
       </c>
       <c r="AC83" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD83" s="3">
         <v>300</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
-      </c>
       <c r="AE83" s="3">
         <v>0</v>
       </c>
@@ -8097,8 +8296,8 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>3</v>
+      <c r="AJ83" s="3">
+        <v>0</v>
       </c>
       <c r="AK83" s="3" t="s">
         <v>3</v>
@@ -8106,8 +8305,11 @@
       <c r="AL83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8216,8 +8418,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8326,8 +8531,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8436,8 +8644,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8546,8 +8757,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8656,118 +8870,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E89" s="3">
         <v>22300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-11600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>62100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-28500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-38800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-40100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-41200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-34300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-29200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-31800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-24200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-29300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-41700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-63300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-27600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-20500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-50200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8806,31 +9026,32 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8845,16 +9066,16 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-300</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
@@ -8866,49 +9087,49 @@
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-100</v>
       </c>
       <c r="AG91" s="3">
         <v>-100</v>
       </c>
       <c r="AH91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>3</v>
+      <c r="AJ91" s="3">
+        <v>0</v>
       </c>
       <c r="AK91" s="3" t="s">
         <v>3</v>
@@ -8916,8 +9137,11 @@
       <c r="AL91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9026,8 +9250,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9136,109 +9363,112 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-51500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>65300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-46800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>25500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>35500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-37900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-42700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>38300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-50000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>47800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>86000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>44800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>68600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-149700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-31200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>88800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>15200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>41400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>29700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-194900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-73900</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>-100</v>
       </c>
       <c r="AG94" s="3">
         <v>-100</v>
       </c>
       <c r="AH94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI94" s="3">
         <v>0</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>3</v>
+      <c r="AJ94" s="3">
+        <v>0</v>
       </c>
       <c r="AK94" s="3" t="s">
         <v>3</v>
@@ -9246,8 +9476,11 @@
       <c r="AL94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9286,8 +9519,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9318,8 +9552,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9396,8 +9630,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9506,8 +9743,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9616,8 +9856,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9726,109 +9969,112 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E100" s="3">
         <v>2800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>146400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>77600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>83200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>156400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>190800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>39900</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
         <v>0</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>3</v>
+      <c r="AJ100" s="3">
+        <v>0</v>
       </c>
       <c r="AK100" s="3" t="s">
         <v>3</v>
@@ -9836,8 +10082,11 @@
       <c r="AL100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9868,8 +10117,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9946,114 +10195,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-26400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>86200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-41800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>33100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>31900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-42100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-53000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>81500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>31000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-59100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-67700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>22000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>48100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>28200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-37600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>17100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>59400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>10700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-216100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>64600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>175800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AL102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="92">
   <si>
     <t>KNSA</t>
   </si>
@@ -656,229 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="40" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="41" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AM7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AN7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AO7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>202100</v>
+      </c>
+      <c r="E8" s="3">
         <v>180900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>156800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>137800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>122500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>112200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>108600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>79900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>83400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>67000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>71500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>48300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>61900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>99100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>27000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>32200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7700</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -894,8 +897,8 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
@@ -933,68 +936,71 @@
       <c r="AN8" s="3">
         <v>0</v>
       </c>
+      <c r="AO8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E9" s="3">
         <v>83600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>71000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>61700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>66100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>49400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>42300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>31400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>26500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>21700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2500</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1049,68 +1055,71 @@
       <c r="AN9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>111200</v>
+      </c>
+      <c r="E10" s="3">
         <v>97300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>85800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>76100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>56500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>62800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>66300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>48500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>56900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>40600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>49800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>33000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>55200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>92200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>22000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>28000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>14800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5200</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1165,8 +1174,11 @@
       <c r="AN10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,124 +1219,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E12" s="3">
         <v>24200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>19300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>35200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>20100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>27400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>23900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>28700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>37400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>31400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>22300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>20900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>22900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>22000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>30800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>59300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>36100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>20600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>17200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>12600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>56400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>14000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>9300</v>
       </c>
-      <c r="AL12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1439,8 +1455,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1477,8 +1496,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1516,8 +1535,8 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
@@ -1528,8 +1547,8 @@
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1555,22 +1574,25 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
         <v>400</v>
       </c>
       <c r="F15" s="3">
+        <v>400</v>
+      </c>
+      <c r="G15" s="3">
         <v>300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>400</v>
       </c>
       <c r="H15" s="3">
         <v>400</v>
@@ -1579,13 +1601,13 @@
         <v>400</v>
       </c>
       <c r="J15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
       </c>
       <c r="L15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M15" s="3">
         <v>600</v>
@@ -1594,7 +1616,7 @@
         <v>600</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1671,8 +1693,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,184 +1735,188 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>182400</v>
+      </c>
+      <c r="E17" s="3">
         <v>156800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>136600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>124500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>141800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>121900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>108700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>96400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>83300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>78000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>74600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>59500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>52700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>46300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>55500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>54900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>42800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>48300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>49300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>52900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>43200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>31900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>29400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>32600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>30400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>39300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>67600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>44100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>26200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>16300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>65400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>16200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>11400</v>
       </c>
-      <c r="AL17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E18" s="3">
         <v>24000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>20200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-19300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>46400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-23300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-36200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-30700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-40600</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1903,47 +1932,50 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-30400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-39300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-67600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-44100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-26200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-21500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-16300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-65400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-16200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-11400</v>
       </c>
-      <c r="AL18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1984,67 +2016,68 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-2300</v>
       </c>
       <c r="G20" s="3">
         <v>-2300</v>
       </c>
       <c r="H20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="I20" s="3">
         <v>-2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-2400</v>
       </c>
       <c r="L20" s="3">
         <v>-2400</v>
       </c>
       <c r="M20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -2061,38 +2094,38 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3">
         <v>1400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>500</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>200</v>
       </c>
       <c r="AK20" s="3">
         <v>200</v>
       </c>
-      <c r="AL20" s="3" t="s">
-        <v>3</v>
+      <c r="AL20" s="3">
+        <v>200</v>
       </c>
       <c r="AM20" s="3" t="s">
         <v>3</v>
@@ -2100,68 +2133,71 @@
       <c r="AN20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E21" s="3">
         <v>27500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>23200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-16600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>47200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-18600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-22600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-35400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-30000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-39800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2177,47 +2213,50 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-28500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-37100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-65400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-42200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-24500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-20400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-64800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-11200</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2254,8 +2293,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2332,219 +2371,225 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E23" s="3">
         <v>27200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>46700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-23300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-36100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-30700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-40500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-49300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-52900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-43200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-31600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-28600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-31500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-29100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-37600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-65800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-42400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-24500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-64900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AL23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E24" s="3">
         <v>8700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-8100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-22800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-16200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-177400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-400</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>-100</v>
       </c>
       <c r="AI24" s="3">
         <v>-100</v>
@@ -2553,10 +2598,10 @@
         <v>-100</v>
       </c>
       <c r="AK24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL24" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>0</v>
       </c>
       <c r="AM24" s="3" t="s">
         <v>3</v>
@@ -2564,8 +2609,11 @@
       <c r="AN24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2680,240 +2728,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E26" s="3">
         <v>18400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>25200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>15000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>224100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-25200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-36300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-30500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-41600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-49500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-53700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-43800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-37500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-26400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-31800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-27100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-37200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-65800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-24400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-64800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AL26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E27" s="3">
         <v>18400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>25200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>15000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>224100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-25200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-36300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-30500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-41600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-49500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-53700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-43800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-37500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-26400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-31800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-27100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-37200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-65800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-24400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-64800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AL27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3028,8 +3085,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3108,8 +3168,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>3</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>3</v>
@@ -3126,12 +3186,12 @@
       <c r="AH29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>3</v>
       </c>
@@ -3144,8 +3204,11 @@
       <c r="AN29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3260,8 +3323,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3376,67 +3442,70 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E32" s="3">
         <v>3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2300</v>
       </c>
       <c r="G32" s="3">
         <v>2300</v>
       </c>
       <c r="H32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I32" s="3">
         <v>2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>2400</v>
       </c>
       <c r="L32" s="3">
         <v>2400</v>
       </c>
       <c r="M32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N32" s="3">
         <v>1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -3453,38 +3522,38 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-500</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>-200</v>
       </c>
       <c r="AK32" s="3">
         <v>-200</v>
       </c>
-      <c r="AL32" s="3" t="s">
-        <v>3</v>
+      <c r="AL32" s="3">
+        <v>-200</v>
       </c>
       <c r="AM32" s="3" t="s">
         <v>3</v>
@@ -3492,124 +3561,130 @@
       <c r="AN32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E33" s="3">
         <v>18400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>25200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>15000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>224100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-25200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-36300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-30500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-41600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-49500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-53700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-43800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-37500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-26400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-31800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-27100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-37200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-65800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-24400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-64900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AL33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3724,245 +3799,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E35" s="3">
         <v>18400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>25200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>15000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>224100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-25200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-36300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-30500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-41600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-49500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-53700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-43800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-37500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-26400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-31800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-27100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-37200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-65800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-24400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-64900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AL35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AM38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AN38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AO38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4003,8 +4087,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4045,107 +4130,108 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>165600</v>
+      </c>
+      <c r="E41" s="3">
         <v>174900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>192000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>157100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>183600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>97400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>99300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>141100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>108000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>117800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>80600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>122700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>175800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>94300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>63300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>122500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>190200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>168000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>119900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>114000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>85900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>123500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>106300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>46900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>68800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>82800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>82600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>72000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>69700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>285500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>221100</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
@@ -4161,104 +4247,107 @@
       <c r="AN41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>248500</v>
+      </c>
+      <c r="E42" s="3">
         <v>177200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>115700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>111200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>60000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>126400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>119500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>72500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>98400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>83300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>72400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>106900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>67900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>25000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>43900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>82300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>59700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>10000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>57900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>144200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>209400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>278500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>128900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>97900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>186500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>189900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>204600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>243900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>235300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>268200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>73700</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4277,68 +4366,71 @@
       <c r="AN42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E43" s="3">
         <v>51700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>31900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>40100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>41700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>20500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>29400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2600</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4354,8 +4446,8 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -4393,71 +4485,74 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E44" s="3">
         <v>41400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>48200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>22100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>26400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>28700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>34900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>27300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>31100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>25600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>24000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>23400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>21600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>14600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>19900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2200</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4473,8 +4568,8 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
@@ -4509,8 +4604,11 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4547,69 +4645,69 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>10500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>9600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>9000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>8400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1300</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4625,107 +4723,110 @@
       <c r="AN45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>527200</v>
+      </c>
+      <c r="E46" s="3">
         <v>475500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>420300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>355900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>331800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>311300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>301000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>270600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>276300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>256100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>246000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>231500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>243100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>241800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>179900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>198800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>196400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>217500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>244800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>275600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>333200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>378400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>264500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>213100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>241600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>268300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>296500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>335000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>313800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>341500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>363900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>222500</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4741,8 +4842,11 @@
       <c r="AN46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4779,8 +4883,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4857,107 +4961,110 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E48" s="3">
         <v>11700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>100</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4973,71 +5080,74 @@
       <c r="AN48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E49" s="3">
         <v>15500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>18800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>19500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>20000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -5053,8 +5163,8 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -5089,8 +5199,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5205,8 +5318,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5321,107 +5437,110 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E52" s="3">
         <v>8300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>8200</v>
       </c>
       <c r="F52" s="3">
         <v>8200</v>
       </c>
       <c r="G52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="H52" s="3">
         <v>10300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>7900</v>
       </c>
       <c r="I52" s="3">
         <v>7900</v>
       </c>
       <c r="J52" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K52" s="3">
         <v>4100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>191300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>191500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6600</v>
-      </c>
-      <c r="U52" s="3">
-        <v>5800</v>
       </c>
       <c r="V52" s="3">
         <v>5800</v>
       </c>
       <c r="W52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="X52" s="3">
         <v>5600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2200</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5437,8 +5556,11 @@
       <c r="AN52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5553,107 +5675,110 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>763600</v>
+      </c>
+      <c r="E54" s="3">
         <v>712300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>661200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>599300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>580600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>555300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>542400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>519700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>526300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>483100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>484300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>442900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>459700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>460000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>210600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>231000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>232800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>252900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>279200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>311200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>349500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>384400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>271400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>226100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>254500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>281800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>308100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>346200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>322000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>347100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>365100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>224800</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5669,8 +5794,11 @@
       <c r="AN54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5711,8 +5839,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5753,107 +5882,108 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>2000</v>
       </c>
       <c r="G57" s="3">
         <v>2000</v>
       </c>
       <c r="H57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I57" s="3">
         <v>8300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2800</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5869,31 +5999,34 @@
       <c r="AN57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2000</v>
       </c>
       <c r="H58" s="3">
         <v>2000</v>
       </c>
       <c r="I58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J58" s="3">
         <v>2100</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2300</v>
       </c>
       <c r="K58" s="3">
         <v>2300</v>
@@ -5902,14 +6035,14 @@
         <v>2300</v>
       </c>
       <c r="M58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N58" s="3">
         <v>2200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3500</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5985,107 +6118,110 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E59" s="3">
         <v>20500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>16100</v>
       </c>
       <c r="H59" s="3">
         <v>16100</v>
       </c>
       <c r="I59" s="3">
+        <v>16100</v>
+      </c>
+      <c r="J59" s="3">
         <v>11500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>39200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>55000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>41000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>47000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>43000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>32800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>34600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>32700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>31300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>18200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>21100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>20800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>30000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>31600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>23400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>22600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>16500</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
@@ -6101,107 +6237,110 @@
       <c r="AN59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>139200</v>
+      </c>
+      <c r="E60" s="3">
         <v>123600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>117800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>97300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>100600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>96000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>84300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>64200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>63700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>53500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>47500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>36600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>56500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>43500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>50400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>44800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>34400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>35500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>31800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>24900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>20600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>27800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>27600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>30200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>36900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>42600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>28000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>23100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>19300</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
@@ -6217,47 +6356,50 @@
       <c r="AN60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E61" s="3">
         <v>7000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -6333,28 +6475,31 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E62" s="3">
         <v>14500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1900</v>
       </c>
       <c r="J62" s="3">
         <v>1900</v>
@@ -6372,67 +6517,67 @@
         <v>1900</v>
       </c>
       <c r="O62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P62" s="3">
         <v>16500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>19500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>100</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>200</v>
       </c>
       <c r="AG62" s="3">
         <v>200</v>
       </c>
       <c r="AH62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI62" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="AI62" s="3">
+        <v>0</v>
       </c>
       <c r="AJ62" s="3" t="s">
         <v>3</v>
@@ -6449,8 +6594,11 @@
       <c r="AN62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6565,8 +6713,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6681,8 +6832,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6797,107 +6951,110 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>196000</v>
+      </c>
+      <c r="E66" s="3">
         <v>177000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>166100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>141800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>142100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>118300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>107300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>87800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>87500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>77900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>72700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>63500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>75900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>57100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>64700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>47800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>38800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>43400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>40500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>37500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>25900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>21000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>20300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>29100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>29900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>32900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>39600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>42700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>28200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>23300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19300</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6913,8 +7070,11 @@
       <c r="AN66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6955,8 +7115,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7071,8 +7232,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7187,8 +7351,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7283,11 +7450,11 @@
         <v>0</v>
       </c>
       <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
         <v>310600</v>
       </c>
-      <c r="AI70" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
@@ -7303,8 +7470,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7419,107 +7589,110 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-462100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-476300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-494800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-512600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-521100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-512300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-499600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-495700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-478000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-503200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-489300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-504300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-492000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-496500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-720600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-700600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-675400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-639100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-608500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-567000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-517500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-463800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-420000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-382500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-356100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-324300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-297200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-194200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-151600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-127200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-107000</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7535,8 +7708,11 @@
       <c r="AN72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7651,8 +7827,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7767,8 +7946,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7883,107 +8065,110 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>567600</v>
+      </c>
+      <c r="E76" s="3">
         <v>535400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>495000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>457500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>438400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>437000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>435100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>431900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>438800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>405100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>411700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>390100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>396100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>384000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>153500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>166200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>185000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>214000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>235800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>270700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>311900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>358500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>250400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>205800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>225400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>251900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>275200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>306500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>279300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>318900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>341800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-105100</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7999,8 +8184,11 @@
       <c r="AN76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8115,245 +8303,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AM80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AN80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AO80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E81" s="3">
         <v>18400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>25200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>15000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>224100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-25200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-36300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-30500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-41600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-49500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-53700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-43800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-37500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-26400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-31800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-27100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-37200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-65800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-24400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-64900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AL81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8394,8 +8591,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8406,13 +8604,13 @@
         <v>400</v>
       </c>
       <c r="F83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G83" s="3">
         <v>500</v>
       </c>
       <c r="H83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I83" s="3">
         <v>600</v>
@@ -8424,22 +8622,22 @@
         <v>600</v>
       </c>
       <c r="L83" s="3">
+        <v>600</v>
+      </c>
+      <c r="M83" s="3">
         <v>500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>700</v>
       </c>
       <c r="N83" s="3">
         <v>700</v>
       </c>
       <c r="O83" s="3">
+        <v>700</v>
+      </c>
+      <c r="P83" s="3">
         <v>600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>700</v>
       </c>
       <c r="R83" s="3">
         <v>700</v>
@@ -8454,10 +8652,10 @@
         <v>700</v>
       </c>
       <c r="V83" s="3">
+        <v>700</v>
+      </c>
+      <c r="W83" s="3">
         <v>300</v>
-      </c>
-      <c r="W83" s="3">
-        <v>600</v>
       </c>
       <c r="X83" s="3">
         <v>600</v>
@@ -8472,7 +8670,7 @@
         <v>600</v>
       </c>
       <c r="AB83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AC83" s="3">
         <v>500</v>
@@ -8481,11 +8679,11 @@
         <v>500</v>
       </c>
       <c r="AE83" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF83" s="3">
         <v>300</v>
       </c>
-      <c r="AF83" s="3">
-        <v>0</v>
-      </c>
       <c r="AG83" s="3">
         <v>0</v>
       </c>
@@ -8501,8 +8699,8 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>3</v>
+      <c r="AL83" s="3">
+        <v>0</v>
       </c>
       <c r="AM83" s="3" t="s">
         <v>3</v>
@@ -8510,8 +8708,11 @@
       <c r="AN83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8626,8 +8827,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8742,8 +8946,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8858,8 +9065,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8974,8 +9184,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9090,124 +9303,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E89" s="3">
         <v>33700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>28100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>22300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>62100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-36800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-18900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-28500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-38800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-40100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-41200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-34300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-29200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-31800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-24200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-29300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-41700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-63300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-27600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-20500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-50200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9248,37 +9467,38 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -9293,16 +9513,16 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-300</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-100</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
@@ -9314,49 +9534,49 @@
         <v>-100</v>
       </c>
       <c r="X91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-100</v>
       </c>
       <c r="AI91" s="3">
         <v>-100</v>
       </c>
       <c r="AJ91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AK91" s="3">
         <v>0</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>3</v>
+      <c r="AL91" s="3">
+        <v>0</v>
       </c>
       <c r="AM91" s="3" t="s">
         <v>3</v>
@@ -9364,8 +9584,11 @@
       <c r="AN91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9480,8 +9703,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9596,115 +9822,118 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-70800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-62800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-51500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>65300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-46800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>25500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>35500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-37900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-42700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>19000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>38300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-50000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>47800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>86000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>44800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>68600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-149700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>88800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>15200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>41400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>29700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-194900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-73900</v>
-      </c>
-      <c r="AH94" s="3">
-        <v>-100</v>
       </c>
       <c r="AI94" s="3">
         <v>-100</v>
       </c>
       <c r="AJ94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AK94" s="3">
         <v>0</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>3</v>
+      <c r="AL94" s="3">
+        <v>0</v>
       </c>
       <c r="AM94" s="3" t="s">
         <v>3</v>
@@ -9712,8 +9941,11 @@
       <c r="AN94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9754,8 +9986,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9792,8 +10025,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9870,8 +10103,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9986,8 +10222,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10102,8 +10341,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10218,115 +10460,118 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E100" s="3">
         <v>11900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>146400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>77600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>83200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>156400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>190800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>39900</v>
       </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
       <c r="AK100" s="3">
         <v>0</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>3</v>
+      <c r="AL100" s="3">
+        <v>0</v>
       </c>
       <c r="AM100" s="3" t="s">
         <v>3</v>
@@ -10334,8 +10579,11 @@
       <c r="AN100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10372,8 +10620,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10450,120 +10698,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>34900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-26400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>86200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-41800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>33100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>31900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-42100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-53000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>81500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>31000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-59100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-67700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>22000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>48100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>28200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-37600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>17100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>59400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-21900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>10700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-216100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>64600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>175800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AN102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="92">
   <si>
     <t>KNSA</t>
   </si>
@@ -656,235 +656,239 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="41" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="42" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AN7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AO7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AP7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>214300</v>
+      </c>
+      <c r="E8" s="3">
         <v>202100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>180900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>156800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>137800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>122500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>112200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>108600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>79900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>83400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>67000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>71500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>48300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>61900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>99100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>27000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>32200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>18700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7700</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -900,8 +904,8 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -939,71 +943,74 @@
       <c r="AO8" s="3">
         <v>0</v>
       </c>
+      <c r="AP8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E9" s="3">
         <v>91000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>83600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>71000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>61700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>66100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>49400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>42300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2500</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1058,71 +1065,74 @@
       <c r="AO9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>117900</v>
+      </c>
+      <c r="E10" s="3">
         <v>111200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>97300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>85800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>76100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>56500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>62800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>66300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>48500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>56900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>40600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>49800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>33000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>55200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>92200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>28000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>14800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5200</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1177,8 +1187,11 @@
       <c r="AO10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1220,127 +1233,131 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E12" s="3">
         <v>34600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>24200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>19300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>35200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>27400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>23900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>28700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>37400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>31400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>22300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>20900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>22900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>22000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>30800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>59300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>36100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>20600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>17200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>12600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>56400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>14000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>9300</v>
       </c>
-      <c r="AM12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1458,8 +1475,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1499,8 +1519,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1538,8 +1558,8 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
@@ -1550,8 +1570,8 @@
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1577,8 +1597,11 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1586,16 +1609,16 @@
         <v>500</v>
       </c>
       <c r="E15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
         <v>400</v>
       </c>
       <c r="G15" s="3">
+        <v>400</v>
+      </c>
+      <c r="H15" s="3">
         <v>300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>400</v>
       </c>
       <c r="I15" s="3">
         <v>400</v>
@@ -1604,13 +1627,13 @@
         <v>400</v>
       </c>
       <c r="K15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L15" s="3">
         <v>500</v>
       </c>
       <c r="M15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="N15" s="3">
         <v>600</v>
@@ -1619,7 +1642,7 @@
         <v>600</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1696,8 +1719,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,190 +1762,194 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E17" s="3">
         <v>182400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>156800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>136600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>124500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>141800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>121900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>108700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>96400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>83300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>78000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>74600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>59500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>52700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>46300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>55500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>54900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>42800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>48300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>49300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>52900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>43200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>31900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>29400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>32600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>30400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>39300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>67600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>44100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>26200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>65400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>16200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>11400</v>
       </c>
-      <c r="AM17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E18" s="3">
         <v>19800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>24000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>20200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-19300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>46400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-19300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-23300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-36200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-30700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-40600</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1935,47 +1965,50 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-30400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-39300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-67600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-44100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-26200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-21500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-16300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-65400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-16200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-11400</v>
       </c>
-      <c r="AM18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2017,70 +2050,71 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2300</v>
       </c>
       <c r="H20" s="3">
         <v>-2300</v>
       </c>
       <c r="I20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-2400</v>
       </c>
       <c r="M20" s="3">
         <v>-2400</v>
       </c>
       <c r="N20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -2097,38 +2131,38 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="3">
         <v>1400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>500</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>200</v>
       </c>
       <c r="AL20" s="3">
         <v>200</v>
       </c>
-      <c r="AM20" s="3" t="s">
-        <v>3</v>
+      <c r="AM20" s="3">
+        <v>200</v>
       </c>
       <c r="AN20" s="3" t="s">
         <v>3</v>
@@ -2136,71 +2170,74 @@
       <c r="AO20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E21" s="3">
         <v>23700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>27500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>23200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>15900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>47200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-18600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-22600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-35400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-30000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-39800</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2216,47 +2253,50 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-28500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-37100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-65400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-42200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-24500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-20400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-64800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-11200</v>
       </c>
-      <c r="AM21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2296,8 +2336,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2374,225 +2414,231 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E23" s="3">
         <v>23300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>27200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>15600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-17000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>46700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-19300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-36100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-30700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-40500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-49300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-52900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-43200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-31600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-28600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-31500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-29100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-37600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-65800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-42400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-24500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-64900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AM23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E24" s="3">
         <v>9100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-8100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-22800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-16200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-177400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-400</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ24" s="3">
         <v>-100</v>
@@ -2601,10 +2647,10 @@
         <v>-100</v>
       </c>
       <c r="AL24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM24" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="AM24" s="3">
+        <v>0</v>
       </c>
       <c r="AN24" s="3" t="s">
         <v>3</v>
@@ -2612,8 +2658,11 @@
       <c r="AO24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2731,246 +2780,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E26" s="3">
         <v>14200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>18400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>25200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>224100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-20000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-25200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-36300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-30500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-41600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-49500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-53700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-37500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-26400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-31800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-27100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-37200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-65800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-24400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-64800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AM26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E27" s="3">
         <v>14200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>25200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>15000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>224100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-25200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-36300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-30500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-41600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-49500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-53700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-37500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-26400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-31800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-27100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-37200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-65800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-24400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-64800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AM27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3088,8 +3146,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3171,8 +3232,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>3</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>3</v>
@@ -3189,12 +3250,12 @@
       <c r="AI29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-100</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>3</v>
       </c>
@@ -3207,8 +3268,11 @@
       <c r="AO29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3326,8 +3390,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3445,70 +3512,73 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>3500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2300</v>
       </c>
       <c r="H32" s="3">
         <v>2300</v>
       </c>
       <c r="I32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J32" s="3">
         <v>2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>2400</v>
       </c>
       <c r="M32" s="3">
         <v>2400</v>
       </c>
       <c r="N32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O32" s="3">
         <v>1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -3525,38 +3595,38 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-500</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>-200</v>
       </c>
       <c r="AL32" s="3">
         <v>-200</v>
       </c>
-      <c r="AM32" s="3" t="s">
-        <v>3</v>
+      <c r="AM32" s="3">
+        <v>-200</v>
       </c>
       <c r="AN32" s="3" t="s">
         <v>3</v>
@@ -3564,127 +3634,133 @@
       <c r="AO32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E33" s="3">
         <v>14200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>18400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>15000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>224100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-25200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-36300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-30500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-41600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-49500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-53700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-37500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-26400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-31800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-27100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-37200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-65800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-42600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-24400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-64900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AM33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3802,251 +3878,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E35" s="3">
         <v>14200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>18400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>15000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>224100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-25200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-36300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-30500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-41600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-49500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-53700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-37500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-26400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-31800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-27100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-37200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-65800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-42600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-24400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-64900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AM35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AN38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AO38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AP38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4088,8 +4173,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4131,110 +4217,111 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E41" s="3">
         <v>165600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>174900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>192000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>157100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>183600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>97400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>99300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>141100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>108000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>117800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>112600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>80600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>122700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>175800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>94300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>63300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>122500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>190200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>168000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>119900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>114000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>85900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>123500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>106300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>46900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>68800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>82800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>82600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>72000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>69700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>285500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>221100</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>3</v>
       </c>
@@ -4250,107 +4337,110 @@
       <c r="AO41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>278100</v>
+      </c>
+      <c r="E42" s="3">
         <v>248500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>177200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>115700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>111200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>60000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>126400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>119500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>72500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>98400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>83300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>72400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>106900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>67900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>25000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>43900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>82300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>59700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>10000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>57900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>144200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>209400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>278500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>128900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>97900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>186500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>189900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>204600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>243900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>235300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>268200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>73700</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4369,71 +4459,74 @@
       <c r="AO42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E43" s="3">
         <v>15600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>51700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>40100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>41700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>21300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>20300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>29400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2600</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4449,8 +4542,8 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -4488,74 +4581,77 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E44" s="3">
         <v>54900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>41400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>48200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>22100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>26400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>28700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>34900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>27300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>31100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>25600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>24000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>23400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>21600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>14600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>19900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2200</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4571,8 +4667,8 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD44" s="3">
-        <v>0</v>
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE44" s="3">
         <v>0</v>
@@ -4607,8 +4703,11 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4648,69 +4747,69 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>10500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>12100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>9600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>8400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4726,110 +4825,113 @@
       <c r="AO45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>594200</v>
+      </c>
+      <c r="E46" s="3">
         <v>527200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>475500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>420300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>355900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>331800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>311300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>301000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>270600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>276300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>256100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>246000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>231500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>243100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>241800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>179900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>198800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>196400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>217500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>244800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>275600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>333200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>378400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>264500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>213100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>241600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>268300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>296500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>335000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>313800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>341500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>363900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>222500</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4845,8 +4947,11 @@
       <c r="AO46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4886,8 +4991,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4964,110 +5069,113 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E48" s="3">
         <v>11800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>100</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>3</v>
       </c>
@@ -5083,74 +5191,77 @@
       <c r="AO48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>18500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>18800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>19300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>19800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>20000</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -5166,8 +5277,8 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE49" s="3">
         <v>0</v>
@@ -5202,8 +5313,11 @@
       <c r="AO49" s="3">
         <v>0</v>
       </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5321,8 +5435,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5440,110 +5557,113 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E52" s="3">
         <v>11300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>8200</v>
       </c>
       <c r="G52" s="3">
         <v>8200</v>
       </c>
       <c r="H52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I52" s="3">
         <v>10300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>7900</v>
       </c>
       <c r="J52" s="3">
         <v>7900</v>
       </c>
       <c r="K52" s="3">
+        <v>7900</v>
+      </c>
+      <c r="L52" s="3">
         <v>4100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>191300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>191500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6600</v>
-      </c>
-      <c r="V52" s="3">
-        <v>5800</v>
       </c>
       <c r="W52" s="3">
         <v>5800</v>
       </c>
       <c r="X52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="Y52" s="3">
         <v>5600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5559,8 +5679,11 @@
       <c r="AO52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5678,110 +5801,113 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>825300</v>
+      </c>
+      <c r="E54" s="3">
         <v>763600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>712300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>661200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>599300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>580600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>555300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>542400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>519700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>526300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>483100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>484300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>442900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>459700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>460000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>210600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>231000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>232800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>252900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>279200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>311200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>349500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>384400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>271400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>226100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>254500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>281800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>308100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>346200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>322000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>347100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>365100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>224800</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5797,8 +5923,11 @@
       <c r="AO54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5840,8 +5969,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5883,110 +6013,111 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2000</v>
       </c>
       <c r="H57" s="3">
         <v>2000</v>
       </c>
       <c r="I57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J57" s="3">
         <v>8300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK57" s="3" t="s">
         <v>3</v>
       </c>
@@ -6002,34 +6133,37 @@
       <c r="AO57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E58" s="3">
         <v>3000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2000</v>
       </c>
       <c r="I58" s="3">
         <v>2000</v>
       </c>
       <c r="J58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K58" s="3">
         <v>2100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2300</v>
       </c>
       <c r="L58" s="3">
         <v>2300</v>
@@ -6038,14 +6172,14 @@
         <v>2300</v>
       </c>
       <c r="N58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O58" s="3">
         <v>2200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3500</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6121,110 +6255,113 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E59" s="3">
         <v>22100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>16100</v>
       </c>
       <c r="I59" s="3">
         <v>16100</v>
       </c>
       <c r="J59" s="3">
+        <v>16100</v>
+      </c>
+      <c r="K59" s="3">
         <v>11500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>39200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>55000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>41000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>47000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>43000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>32800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>34600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>32700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>31300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>18200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>22100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>21100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>20800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>30000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>31600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>23400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>22600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>16500</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK59" s="3" t="s">
         <v>3</v>
       </c>
@@ -6240,110 +6377,113 @@
       <c r="AO59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E60" s="3">
         <v>139200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>123600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>117800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>97300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>100600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>96000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>84300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>64200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>63700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>53500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>47500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>36600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>47100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>56500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>43500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>50400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>44800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>34400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>35500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>31800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>24900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>20600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>19300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>27800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>27600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>30200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>36900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>42600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>28000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>23100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>19300</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK60" s="3" t="s">
         <v>3</v>
       </c>
@@ -6359,50 +6499,53 @@
       <c r="AO60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E61" s="3">
         <v>6500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6478,31 +6621,34 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E62" s="3">
         <v>18500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1900</v>
       </c>
       <c r="K62" s="3">
         <v>1900</v>
@@ -6520,67 +6666,67 @@
         <v>1900</v>
       </c>
       <c r="P62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q62" s="3">
         <v>16500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>19500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>100</v>
-      </c>
-      <c r="AG62" s="3">
-        <v>200</v>
       </c>
       <c r="AH62" s="3">
         <v>200</v>
       </c>
       <c r="AI62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ62" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
       </c>
       <c r="AK62" s="3" t="s">
         <v>3</v>
@@ -6597,8 +6743,11 @@
       <c r="AO62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6716,8 +6865,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6835,8 +6987,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6954,110 +7109,113 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>219600</v>
+      </c>
+      <c r="E66" s="3">
         <v>196000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>177000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>166100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>141800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>142100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>118300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>107300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>87800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>87500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>77900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>72700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>63500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>75900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>57100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>64700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>47800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>38800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>43400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>40500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>37500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>25900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>21000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>20300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>29100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>29900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>32900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>39600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>42700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>28200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>23300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>19300</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>3</v>
       </c>
@@ -7073,8 +7231,11 @@
       <c r="AO66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7116,8 +7277,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7235,8 +7397,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7354,8 +7519,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7453,11 +7621,11 @@
         <v>0</v>
       </c>
       <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
         <v>310600</v>
       </c>
-      <c r="AJ70" s="3">
-        <v>0</v>
-      </c>
       <c r="AK70" s="3">
         <v>0</v>
       </c>
@@ -7473,8 +7641,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7592,110 +7763,113 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-439500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-462100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-476300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-494800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-512600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-521100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-512300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-499600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-495700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-478000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-503200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-489300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-504300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-492000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-496500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-720600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-700600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-675400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-639100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-608500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-567000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-517500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-463800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-420000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-382500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-356100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-324300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-297200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-194200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-151600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-127200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-107000</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7711,8 +7885,11 @@
       <c r="AO72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7830,8 +8007,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7949,8 +8129,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8068,110 +8251,113 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>605700</v>
+      </c>
+      <c r="E76" s="3">
         <v>567600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>535400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>495000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>457500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>438400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>437000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>435100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>431900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>438800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>405100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>411700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>390100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>396100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>384000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>153500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>166200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>185000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>214000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>235800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>270700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>311900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>358500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>250400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>205800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>225400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>251900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>275200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>306500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>279300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>318900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>341800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-105100</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>3</v>
       </c>
@@ -8187,8 +8373,11 @@
       <c r="AO76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8306,251 +8495,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AN80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AO80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AP80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E81" s="3">
         <v>14200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>18400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>15000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>224100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-25200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-36300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-30500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-41600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-49500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-53700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-37500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-26400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-31800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-27100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-37200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-65800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-42600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-24400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-64900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AM81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8592,13 +8790,14 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
         <v>400</v>
@@ -8607,13 +8806,13 @@
         <v>400</v>
       </c>
       <c r="G83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H83" s="3">
         <v>500</v>
       </c>
       <c r="I83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J83" s="3">
         <v>600</v>
@@ -8625,22 +8824,22 @@
         <v>600</v>
       </c>
       <c r="M83" s="3">
+        <v>600</v>
+      </c>
+      <c r="N83" s="3">
         <v>500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>700</v>
       </c>
       <c r="O83" s="3">
         <v>700</v>
       </c>
       <c r="P83" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>700</v>
       </c>
       <c r="S83" s="3">
         <v>700</v>
@@ -8655,10 +8854,10 @@
         <v>700</v>
       </c>
       <c r="W83" s="3">
+        <v>700</v>
+      </c>
+      <c r="X83" s="3">
         <v>300</v>
-      </c>
-      <c r="X83" s="3">
-        <v>600</v>
       </c>
       <c r="Y83" s="3">
         <v>600</v>
@@ -8673,7 +8872,7 @@
         <v>600</v>
       </c>
       <c r="AC83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AD83" s="3">
         <v>500</v>
@@ -8682,11 +8881,11 @@
         <v>500</v>
       </c>
       <c r="AF83" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG83" s="3">
         <v>300</v>
       </c>
-      <c r="AG83" s="3">
-        <v>0</v>
-      </c>
       <c r="AH83" s="3">
         <v>0</v>
       </c>
@@ -8702,8 +8901,8 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
-      <c r="AM83" s="3" t="s">
-        <v>3</v>
+      <c r="AM83" s="3">
+        <v>0</v>
       </c>
       <c r="AN83" s="3" t="s">
         <v>3</v>
@@ -8711,8 +8910,11 @@
       <c r="AO83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8830,8 +9032,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8949,8 +9154,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9068,8 +9276,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9187,8 +9398,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9306,127 +9520,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E89" s="3">
         <v>53900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>33700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>28100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>22300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>18800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>62100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-36800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-18900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-28500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-38800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-40100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-41200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-34300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-29200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-31800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-24200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-29300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-41700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-63300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-27600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-20500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-15000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-50200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AM89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9468,40 +9688,41 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -9516,16 +9737,16 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-300</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-100</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
@@ -9537,49 +9758,49 @@
         <v>-100</v>
       </c>
       <c r="Y91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AI91" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ91" s="3">
         <v>-100</v>
       </c>
       <c r="AK91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AL91" s="3">
         <v>0</v>
       </c>
-      <c r="AM91" s="3" t="s">
-        <v>3</v>
+      <c r="AM91" s="3">
+        <v>0</v>
       </c>
       <c r="AN91" s="3" t="s">
         <v>3</v>
@@ -9587,8 +9808,11 @@
       <c r="AO91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9706,8 +9930,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9825,118 +10052,121 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-70800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-62800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-51500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>65300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-46800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>25500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>35500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-37900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>19000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>38300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-22700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-50000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>47800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>86000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>44800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>68600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-149700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>88800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>15200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>41400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>29700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-194900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-73900</v>
-      </c>
-      <c r="AI94" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ94" s="3">
         <v>-100</v>
       </c>
       <c r="AK94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AL94" s="3">
         <v>0</v>
       </c>
-      <c r="AM94" s="3" t="s">
-        <v>3</v>
+      <c r="AM94" s="3">
+        <v>0</v>
       </c>
       <c r="AN94" s="3" t="s">
         <v>3</v>
@@ -9944,8 +10174,11 @@
       <c r="AO94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9987,8 +10220,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10028,8 +10262,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10106,8 +10340,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10225,8 +10462,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10344,8 +10584,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10463,118 +10706,121 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E100" s="3">
         <v>7700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>11900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>146400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>77600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>83200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>156400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>190800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>39900</v>
       </c>
-      <c r="AK100" s="3">
-        <v>0</v>
-      </c>
       <c r="AL100" s="3">
         <v>0</v>
       </c>
-      <c r="AM100" s="3" t="s">
-        <v>3</v>
+      <c r="AM100" s="3">
+        <v>0</v>
       </c>
       <c r="AN100" s="3" t="s">
         <v>3</v>
@@ -10582,8 +10828,11 @@
       <c r="AO100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AP100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10623,8 +10872,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10701,123 +10950,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>34900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-26400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>86200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-41800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>33100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>31900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-42100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>81500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>31000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-59100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-67700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>22000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>48100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>28200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-37600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>17100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>59400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-21900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>10700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-216100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>64600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>175800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AM102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AN102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AO102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
